--- a/Config/HeroConfig.xlsx
+++ b/Config/HeroConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="12645" windowHeight="9090"/>
+    <workbookView windowWidth="15690" windowHeight="14160"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="47">
   <si>
     <t>##var</t>
   </si>
@@ -88,6 +88,9 @@
     <t>1000</t>
   </si>
   <si>
+    <t>Adventurer1</t>
+  </si>
+  <si>
     <t>平平无奇之人</t>
   </si>
   <si>
@@ -97,6 +100,9 @@
     <t>大壮</t>
   </si>
   <si>
+    <t>Warrior1</t>
+  </si>
+  <si>
     <t>受到的伤害-25%</t>
   </si>
   <si>
@@ -109,52 +115,58 @@
     <t>造成的伤害+25%</t>
   </si>
   <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>多面手</t>
+  </si>
+  <si>
+    <t>攻击时,对其他敌人造成30%的伤害</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>射手</t>
+  </si>
+  <si>
+    <t>Ranger1</t>
+  </si>
+  <si>
+    <t>攻击时,有50%概率额外进行一次攻击</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>大嗓门</t>
+  </si>
+  <si>
+    <t>Mage1</t>
+  </si>
+  <si>
+    <t>攻击时,对所有人造成1次原伤害50%的群体伤害</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>暴发户</t>
+  </si>
+  <si>
+    <t>初始拥有一定资金</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>流浪汉</t>
+  </si>
+  <si>
+    <t>在闷注获胜后,获得的积分数量翻倍</t>
+  </si>
+  <si>
     <t>9</t>
-  </si>
-  <si>
-    <t>多面手</t>
-  </si>
-  <si>
-    <t>攻击时,对其他敌人造成30%的伤害</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>老师傅</t>
-  </si>
-  <si>
-    <t>攻击时,有50%概率额外进行一次攻击</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>大嗓门</t>
-  </si>
-  <si>
-    <t>攻击时,对所有人造成1次原伤害50%的群体伤害</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>暴发户</t>
-  </si>
-  <si>
-    <t>初始拥有一定资金</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>流浪汉</t>
-  </si>
-  <si>
-    <t>在闷注获胜后,获得的积分数量翻倍</t>
-  </si>
-  <si>
-    <t>12</t>
   </si>
   <si>
     <t>赌神</t>
@@ -1139,7 +1151,8 @@
   <cols>
     <col min="1" max="1" width="9" style="1"/>
     <col min="2" max="2" width="4.01666666666667" style="1" customWidth="1"/>
-    <col min="3" max="5" width="9" style="1"/>
+    <col min="3" max="4" width="9" style="1"/>
+    <col min="5" max="5" width="12.0583333333333" style="1" customWidth="1"/>
     <col min="6" max="6" width="10.3166666666667" style="2" customWidth="1"/>
     <col min="7" max="7" width="14.3416666666667" style="1" customWidth="1"/>
     <col min="8" max="8" width="34.75" style="1" customWidth="1"/>
@@ -1226,123 +1239,149 @@
       <c r="D5" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E5" s="1"/>
+      <c r="E5" s="1" t="s">
+        <v>18</v>
+      </c>
       <c r="F5" s="1"/>
       <c r="G5" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H5" s="1"/>
     </row>
     <row r="6" spans="1:8">
       <c r="B6" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>17</v>
       </c>
+      <c r="E6" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="G6" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="B7" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>17</v>
       </c>
+      <c r="E7" s="1" t="s">
+        <v>18</v>
+      </c>
       <c r="G7" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="B8" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>17</v>
       </c>
+      <c r="E8" s="1" t="s">
+        <v>18</v>
+      </c>
       <c r="G8" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="B9" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>17</v>
       </c>
+      <c r="E9" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="G9" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="B10" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>17</v>
       </c>
+      <c r="E10" s="1" t="s">
+        <v>36</v>
+      </c>
       <c r="G10" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="B11" s="1" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>17</v>
       </c>
+      <c r="E11" s="1" t="s">
+        <v>18</v>
+      </c>
       <c r="G11" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="B12" s="1" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>17</v>
       </c>
+      <c r="E12" s="1" t="s">
+        <v>18</v>
+      </c>
       <c r="G12" s="1" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="B13" s="1" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>17</v>
       </c>
+      <c r="E13" s="1" t="s">
+        <v>18</v>
+      </c>
       <c r="G13" s="1" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>

--- a/Config/HeroConfig.xlsx
+++ b/Config/HeroConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="15690" windowHeight="14160"/>
+    <workbookView windowWidth="16275" windowHeight="15945"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="49">
   <si>
     <t>##var</t>
   </si>
@@ -52,6 +52,9 @@
     <t>HeroEntry</t>
   </si>
   <si>
+    <t>UnlockCondition</t>
+  </si>
+  <si>
     <t>Desc</t>
   </si>
   <si>
@@ -74,6 +77,9 @@
   </si>
   <si>
     <t>英雄机制</t>
+  </si>
+  <si>
+    <t>解锁难度条件</t>
   </si>
   <si>
     <t>描述</t>
@@ -1146,20 +1152,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
+  <dimension ref="A1:I13"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
     <col min="2" max="2" width="4.01666666666667" style="1" customWidth="1"/>
     <col min="3" max="4" width="9" style="1"/>
     <col min="5" max="5" width="12.0583333333333" style="1" customWidth="1"/>
     <col min="6" max="6" width="10.3166666666667" style="2" customWidth="1"/>
-    <col min="7" max="7" width="14.3416666666667" style="1" customWidth="1"/>
-    <col min="8" max="8" width="34.75" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="9" style="1"/>
+    <col min="7" max="7" width="15.75" style="1" customWidth="1"/>
+    <col min="8" max="8" width="14.3416666666667" style="1" customWidth="1"/>
+    <col min="9" max="9" width="34.75" style="1" customWidth="1"/>
+    <col min="10" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1181,207 +1188,241 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="E2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>9</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>8</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>9</v>
       </c>
+      <c r="H2" s="2" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>16</v>
       </c>
     </row>
-    <row r="5" customFormat="1" spans="1:8">
+    <row r="5" customFormat="1" spans="1:9">
       <c r="A5" s="1"/>
       <c r="B5" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I5" s="1"/>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="B6" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G6" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E5" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1" t="s">
+      <c r="H6" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="B7" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="H5" s="1"/>
+      <c r="E7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>28</v>
+      </c>
     </row>
-    <row r="6" spans="1:8">
-      <c r="B6" s="1" t="s">
+    <row r="8" spans="1:9">
+      <c r="B8" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>23</v>
+      <c r="G8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
-      <c r="B7" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>26</v>
+    <row r="9" spans="1:9">
+      <c r="B9" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>35</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
-      <c r="B8" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>29</v>
+    <row r="10" spans="1:9">
+      <c r="B10" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>39</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
-      <c r="B9" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>33</v>
+    <row r="11" spans="1:9">
+      <c r="B11" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>42</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
-      <c r="B10" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>37</v>
+    <row r="12" spans="1:9">
+      <c r="B12" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>45</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
-      <c r="B11" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8">
-      <c r="B12" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G12" s="1" t="s">
+    <row r="13" spans="1:9">
+      <c r="B13" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G13" s="1" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="13" spans="1:8">
-      <c r="B13" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>46</v>
+      <c r="H13" s="1" t="s">
+        <v>48</v>
       </c>
     </row>
   </sheetData>

--- a/Config/HeroConfig.xlsx
+++ b/Config/HeroConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="16275" windowHeight="15945"/>
+    <workbookView windowWidth="16965" windowHeight="13155"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -49,7 +49,7 @@
     <t>Icon</t>
   </si>
   <si>
-    <t>HeroEntry</t>
+    <t>HeroEntryId</t>
   </si>
   <si>
     <t>UnlockCondition</t>
@@ -76,7 +76,7 @@
     <t>形象icon</t>
   </si>
   <si>
-    <t>英雄机制</t>
+    <t>英雄机制id</t>
   </si>
   <si>
     <t>解锁难度条件</t>
@@ -1159,7 +1159,7 @@
     <col min="2" max="2" width="4.01666666666667" style="1" customWidth="1"/>
     <col min="3" max="4" width="9" style="1"/>
     <col min="5" max="5" width="12.0583333333333" style="1" customWidth="1"/>
-    <col min="6" max="6" width="10.3166666666667" style="2" customWidth="1"/>
+    <col min="6" max="6" width="11.7416666666667" style="2" customWidth="1"/>
     <col min="7" max="7" width="15.75" style="1" customWidth="1"/>
     <col min="8" max="8" width="14.3416666666667" style="1" customWidth="1"/>
     <col min="9" max="9" width="34.75" style="1" customWidth="1"/>
@@ -1278,6 +1278,9 @@
       <c r="E6" s="1" t="s">
         <v>24</v>
       </c>
+      <c r="F6" s="2">
+        <v>10001</v>
+      </c>
       <c r="G6" s="1" t="s">
         <v>17</v>
       </c>
@@ -1298,6 +1301,9 @@
       <c r="E7" s="1" t="s">
         <v>20</v>
       </c>
+      <c r="F7" s="2">
+        <v>10002</v>
+      </c>
       <c r="G7" s="1" t="s">
         <v>22</v>
       </c>
@@ -1318,6 +1324,9 @@
       <c r="E8" s="1" t="s">
         <v>20</v>
       </c>
+      <c r="F8" s="2">
+        <v>10003</v>
+      </c>
       <c r="G8" s="1" t="s">
         <v>26</v>
       </c>
@@ -1338,6 +1347,9 @@
       <c r="E9" s="1" t="s">
         <v>34</v>
       </c>
+      <c r="F9" s="2">
+        <v>10004</v>
+      </c>
       <c r="G9" s="1" t="s">
         <v>29</v>
       </c>
@@ -1358,6 +1370,9 @@
       <c r="E10" s="1" t="s">
         <v>38</v>
       </c>
+      <c r="F10" s="2">
+        <v>10005</v>
+      </c>
       <c r="G10" s="1" t="s">
         <v>32</v>
       </c>
@@ -1378,6 +1393,9 @@
       <c r="E11" s="1" t="s">
         <v>20</v>
       </c>
+      <c r="F11" s="2">
+        <v>10006</v>
+      </c>
       <c r="G11" s="1" t="s">
         <v>36</v>
       </c>
@@ -1398,6 +1416,9 @@
       <c r="E12" s="1" t="s">
         <v>20</v>
       </c>
+      <c r="F12" s="2">
+        <v>10007</v>
+      </c>
       <c r="G12" s="1" t="s">
         <v>40</v>
       </c>
@@ -1417,6 +1438,9 @@
       </c>
       <c r="E13" s="1" t="s">
         <v>20</v>
+      </c>
+      <c r="F13" s="2">
+        <v>10008</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>43</v>

--- a/Config/HeroConfig.xlsx
+++ b/Config/HeroConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="16965" windowHeight="13155"/>
+    <workbookView windowWidth="18270" windowHeight="13050"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="52">
   <si>
     <t>##var</t>
   </si>
@@ -46,6 +46,9 @@
     <t>Hp</t>
   </si>
   <si>
+    <t>HeroDamage</t>
+  </si>
+  <si>
     <t>Icon</t>
   </si>
   <si>
@@ -73,6 +76,9 @@
     <t>生命值</t>
   </si>
   <si>
+    <t>攻击力</t>
+  </si>
+  <si>
     <t>形象icon</t>
   </si>
   <si>
@@ -92,6 +98,9 @@
   </si>
   <si>
     <t>1000</t>
+  </si>
+  <si>
+    <t>10</t>
   </si>
   <si>
     <t>Adventurer1</t>
@@ -1152,21 +1161,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
     <col min="2" max="2" width="4.01666666666667" style="1" customWidth="1"/>
     <col min="3" max="4" width="9" style="1"/>
-    <col min="5" max="5" width="12.0583333333333" style="1" customWidth="1"/>
-    <col min="6" max="6" width="11.7416666666667" style="2" customWidth="1"/>
-    <col min="7" max="7" width="15.75" style="1" customWidth="1"/>
-    <col min="8" max="8" width="14.3416666666667" style="1" customWidth="1"/>
-    <col min="9" max="9" width="34.75" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="9" style="1"/>
+    <col min="5" max="6" width="12.0583333333333" style="1" customWidth="1"/>
+    <col min="7" max="7" width="11.7416666666667" style="2" customWidth="1"/>
+    <col min="8" max="8" width="15.75" style="1" customWidth="1"/>
+    <col min="9" max="9" width="14.3416666666667" style="1" customWidth="1"/>
+    <col min="10" max="10" width="34.75" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1182,271 +1191,307 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:10">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>9</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>9</v>
+      <c r="F2" s="1" t="s">
+        <v>11</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>10</v>
       </c>
+      <c r="I2" s="2" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:10">
       <c r="A3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="G3" s="2" t="s">
+        <v>16</v>
+      </c>
       <c r="H3" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
-    <row r="5" customFormat="1" spans="1:9">
+    <row r="5" customFormat="1" spans="1:10">
       <c r="A5" s="1"/>
       <c r="B5" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J5" s="1"/>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="B6" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G6" s="2">
+        <v>10001</v>
+      </c>
+      <c r="H6" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E5" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1" t="s">
+      <c r="I6" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="B7" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="I5" s="1"/>
+      <c r="E7" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G7" s="2">
+        <v>10002</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>31</v>
+      </c>
     </row>
-    <row r="6" spans="1:9">
-      <c r="B6" s="1" t="s">
+    <row r="8" spans="1:10">
+      <c r="B8" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="F8" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F6" s="2">
-        <v>10001</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>25</v>
+      <c r="G8" s="2">
+        <v>10003</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>34</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
-      <c r="B7" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F7" s="2">
-        <v>10002</v>
-      </c>
-      <c r="G7" s="1" t="s">
+    <row r="9" spans="1:10">
+      <c r="B9" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E9" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="H7" s="1" t="s">
-        <v>28</v>
+      <c r="F9" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G9" s="2">
+        <v>10004</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:9">
-      <c r="B8" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F8" s="2">
-        <v>10003</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>31</v>
+    <row r="10" spans="1:10">
+      <c r="B10" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G10" s="2">
+        <v>10005</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>42</v>
       </c>
     </row>
-    <row r="9" spans="1:9">
-      <c r="B9" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F9" s="2">
-        <v>10004</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>35</v>
+    <row r="11" spans="1:10">
+      <c r="B11" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G11" s="2">
+        <v>10006</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>45</v>
       </c>
     </row>
-    <row r="10" spans="1:9">
-      <c r="B10" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F10" s="2">
-        <v>10005</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>39</v>
+    <row r="12" spans="1:10">
+      <c r="B12" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G12" s="2">
+        <v>10007</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>48</v>
       </c>
     </row>
-    <row r="11" spans="1:9">
-      <c r="B11" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F11" s="2">
-        <v>10006</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9">
-      <c r="B12" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F12" s="2">
-        <v>10007</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9">
+    <row r="13" spans="1:10">
       <c r="B13" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G13" s="2">
+        <v>10008</v>
+      </c>
+      <c r="H13" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C13" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F13" s="2">
-        <v>10008</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="H13" s="1" t="s">
-        <v>48</v>
+      <c r="I13" s="1" t="s">
+        <v>51</v>
       </c>
     </row>
   </sheetData>

--- a/Config/HeroConfig.xlsx
+++ b/Config/HeroConfig.xlsx
@@ -97,7 +97,7 @@
     <t>平凡之人</t>
   </si>
   <si>
-    <t>1000</t>
+    <t>100</t>
   </si>
   <si>
     <t>10</t>

--- a/Config/HeroConfig.xlsx
+++ b/Config/HeroConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="18270" windowHeight="13050"/>
+    <workbookView windowWidth="18270" windowHeight="14775"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -166,7 +166,7 @@
     <t>7</t>
   </si>
   <si>
-    <t>暴发户</t>
+    <t>富豪</t>
   </si>
   <si>
     <t>初始拥有一定资金</t>
@@ -175,7 +175,7 @@
     <t>8</t>
   </si>
   <si>
-    <t>流浪汉</t>
+    <t>武林高手</t>
   </si>
   <si>
     <t>在闷注获胜后,获得的积分数量翻倍</t>

--- a/Config/HeroConfig.xlsx
+++ b/Config/HeroConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="18270" windowHeight="14775"/>
+    <workbookView windowWidth="11250" windowHeight="14775"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="53">
   <si>
     <t>##var</t>
   </si>
@@ -97,24 +97,30 @@
     <t>平凡之人</t>
   </si>
   <si>
+    <t>200</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>Adventurer1</t>
+  </si>
+  <si>
+    <t>平平无奇之人</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>大壮</t>
+  </si>
+  <si>
     <t>100</t>
   </si>
   <si>
     <t>10</t>
   </si>
   <si>
-    <t>Adventurer1</t>
-  </si>
-  <si>
-    <t>平平无奇之人</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>大壮</t>
-  </si>
-  <si>
     <t>Warrior1</t>
   </si>
   <si>
@@ -161,9 +167,6 @@
   </si>
   <si>
     <t>攻击时,对所有人造成1次原伤害50%的群体伤害</t>
-  </si>
-  <si>
-    <t>7</t>
   </si>
   <si>
     <t>富豪</t>
@@ -1294,13 +1297,13 @@
         <v>26</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G6" s="2">
         <v>10001</v>
@@ -1309,21 +1312,21 @@
         <v>19</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="B7" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>23</v>
@@ -1335,21 +1338,21 @@
         <v>25</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="B8" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>23</v>
@@ -1358,76 +1361,76 @@
         <v>10003</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="B9" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G9" s="2">
         <v>10004</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="B10" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G10" s="2">
         <v>10005</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="B11" s="1" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>23</v>
@@ -1436,24 +1439,24 @@
         <v>10006</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="B12" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>23</v>
@@ -1462,24 +1465,24 @@
         <v>10007</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="B13" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>23</v>
@@ -1488,10 +1491,10 @@
         <v>10008</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>

--- a/Config/HeroConfig.xlsx
+++ b/Config/HeroConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="11250" windowHeight="14775"/>
+    <workbookView windowWidth="15495" windowHeight="9645"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="67">
   <si>
     <t>##var</t>
   </si>
@@ -49,6 +49,9 @@
     <t>HeroDamage</t>
   </si>
   <si>
+    <t>Critical</t>
+  </si>
+  <si>
     <t>Icon</t>
   </si>
   <si>
@@ -70,6 +73,9 @@
     <t>string</t>
   </si>
   <si>
+    <t>float</t>
+  </si>
+  <si>
     <t>名字</t>
   </si>
   <si>
@@ -79,6 +85,9 @@
     <t>攻击力</t>
   </si>
   <si>
+    <t>暴击率</t>
+  </si>
+  <si>
     <t>形象icon</t>
   </si>
   <si>
@@ -103,6 +112,9 @@
     <t>7</t>
   </si>
   <si>
+    <t>0</t>
+  </si>
+  <si>
     <t>Adventurer1</t>
   </si>
   <si>
@@ -115,34 +127,43 @@
     <t>大壮</t>
   </si>
   <si>
-    <t>100</t>
+    <t>170</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>Warrior1</t>
+  </si>
+  <si>
+    <t>受到的伤害-20%</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>狠人</t>
+  </si>
+  <si>
+    <t>0.05</t>
+  </si>
+  <si>
+    <t>造成的伤害+10%,且拥有5%暴击率</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>多面手</t>
+  </si>
+  <si>
+    <t>160</t>
   </si>
   <si>
     <t>10</t>
   </si>
   <si>
-    <t>Warrior1</t>
-  </si>
-  <si>
-    <t>受到的伤害-25%</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>狠人</t>
-  </si>
-  <si>
-    <t>造成的伤害+25%</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>多面手</t>
-  </si>
-  <si>
-    <t>攻击时,对其他敌人造成30%的伤害</t>
+    <t>攻击时,对其他人造成30%的伤害</t>
   </si>
   <si>
     <t>5</t>
@@ -154,7 +175,7 @@
     <t>Ranger1</t>
   </si>
   <si>
-    <t>攻击时,有50%概率额外进行一次攻击</t>
+    <t>攻击时,有50%概率额外攻击1次</t>
   </si>
   <si>
     <t>6</t>
@@ -166,13 +187,13 @@
     <t>Mage1</t>
   </si>
   <si>
-    <t>攻击时,对所有人造成1次原伤害50%的群体伤害</t>
+    <t>攻击时,对所有人造成50%的群体伤害</t>
   </si>
   <si>
     <t>富豪</t>
   </si>
   <si>
-    <t>初始拥有一定资金</t>
+    <t>初始拥有20资金</t>
   </si>
   <si>
     <t>8</t>
@@ -181,16 +202,37 @@
     <t>武林高手</t>
   </si>
   <si>
-    <t>在闷注获胜后,获得的积分数量翻倍</t>
-  </si>
-  <si>
-    <t>9</t>
+    <t>承受伤害时有25%概率免疫伤害,且初始拥有5%的暴击率</t>
   </si>
   <si>
     <t>赌神</t>
   </si>
   <si>
-    <t>拿到非散牌的概率提高</t>
+    <t>额外拥有1次搓牌的机会</t>
+  </si>
+  <si>
+    <t>暴发户</t>
+  </si>
+  <si>
+    <t>商店里刷到史诗及以上品质的遗物概率提高5%</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>关系户</t>
+  </si>
+  <si>
+    <t>商店中的所有遗物的购买价格打八折</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>经济教授</t>
+  </si>
+  <si>
+    <t>结算伤害后获得的金币数量+10%</t>
   </si>
 </sst>
 </file>
@@ -1164,21 +1206,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="9" style="1"/>
+    <col min="1" max="1" width="5.20833333333333" style="1" customWidth="1"/>
     <col min="2" max="2" width="4.01666666666667" style="1" customWidth="1"/>
-    <col min="3" max="4" width="9" style="1"/>
-    <col min="5" max="6" width="12.0583333333333" style="1" customWidth="1"/>
-    <col min="7" max="7" width="11.7416666666667" style="2" customWidth="1"/>
-    <col min="8" max="8" width="15.75" style="1" customWidth="1"/>
-    <col min="9" max="9" width="14.3416666666667" style="1" customWidth="1"/>
-    <col min="10" max="10" width="34.75" style="1" customWidth="1"/>
-    <col min="11" max="16384" width="9" style="1"/>
+    <col min="3" max="3" width="9" style="1"/>
+    <col min="4" max="4" width="6.08333333333333" style="1" customWidth="1"/>
+    <col min="5" max="5" width="10.3166666666667" style="1" customWidth="1"/>
+    <col min="6" max="6" width="9.00833333333333" style="1" customWidth="1"/>
+    <col min="7" max="7" width="12.0583333333333" style="1" customWidth="1"/>
+    <col min="8" max="8" width="11.7416666666667" style="2" customWidth="1"/>
+    <col min="9" max="9" width="12.7166666666667" style="1" customWidth="1"/>
+    <col min="10" max="10" width="14.3416666666667" style="1" customWidth="1"/>
+    <col min="11" max="11" width="34.75" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1197,304 +1242,427 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:11">
       <c r="A2" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>10</v>
-      </c>
       <c r="E2" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" s="2" t="s">
         <v>11</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>10</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>11</v>
       </c>
+      <c r="J2" s="2" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:11">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H3" s="1" t="s">
         <v>17</v>
       </c>
+      <c r="G3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>19</v>
+      </c>
       <c r="I3" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>21</v>
       </c>
     </row>
-    <row r="5" customFormat="1" spans="1:10">
+    <row r="5" customFormat="1" spans="1:11">
       <c r="A5" s="1"/>
       <c r="B5" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E5" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="K5" s="1"/>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="B6" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H6" s="2">
+        <v>10001</v>
+      </c>
+      <c r="I6" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F5" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1" t="s">
+      <c r="J6" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="B7" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J5" s="1"/>
+      <c r="E7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H7" s="2">
+        <v>10002</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>38</v>
+      </c>
     </row>
-    <row r="6" spans="1:10">
-      <c r="B6" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" s="1" t="s">
+    <row r="8" spans="1:11">
+      <c r="B8" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="G8" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G6" s="2">
-        <v>10001</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>30</v>
+      <c r="H8" s="2">
+        <v>10003</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>43</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
-      <c r="B7" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G7" s="2">
-        <v>10002</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>33</v>
+    <row r="9" spans="1:11">
+      <c r="B9" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="H9" s="2">
+        <v>10004</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>47</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
-      <c r="B8" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G8" s="2">
-        <v>10003</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="B9" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="G9" s="2">
-        <v>10004</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:11">
       <c r="B10" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="E10" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D10" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>28</v>
-      </c>
       <c r="F10" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="G10" s="2">
+        <v>26</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H10" s="2">
         <v>10005</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>37</v>
       </c>
       <c r="I10" s="1" t="s">
         <v>44</v>
       </c>
+      <c r="J10" s="1" t="s">
+        <v>51</v>
+      </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:11">
       <c r="B11" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="D11" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G11" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E11" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G11" s="2">
+      <c r="H11" s="2">
         <v>10006</v>
       </c>
-      <c r="H11" s="1" t="s">
-        <v>41</v>
-      </c>
       <c r="I11" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>53</v>
       </c>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:11">
       <c r="B12" s="1" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="D12" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G12" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E12" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G12" s="2">
+      <c r="H12" s="2">
         <v>10007</v>
       </c>
-      <c r="H12" s="1" t="s">
-        <v>22</v>
-      </c>
       <c r="I12" s="1" t="s">
-        <v>49</v>
+        <v>25</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>56</v>
       </c>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:11">
       <c r="B13" s="1" t="s">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="D13" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G13" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E13" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G13" s="2">
+      <c r="H13" s="2">
         <v>10008</v>
       </c>
-      <c r="H13" s="1" t="s">
-        <v>47</v>
-      </c>
       <c r="I13" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="B14" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H14" s="2">
+        <v>10009</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="B15" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C15" t="s">
+        <v>62</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H15" s="2">
+        <v>10010</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="B16" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H16" s="2">
+        <v>10011</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>66</v>
       </c>
     </row>
   </sheetData>

--- a/Config/HeroConfig.xlsx
+++ b/Config/HeroConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="15495" windowHeight="9645"/>
+    <workbookView windowWidth="14850" windowHeight="9750"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="69">
   <si>
     <t>##var</t>
   </si>
@@ -52,6 +52,9 @@
     <t>Critical</t>
   </si>
   <si>
+    <t>CriticalDamage</t>
+  </si>
+  <si>
     <t>Icon</t>
   </si>
   <si>
@@ -88,6 +91,9 @@
     <t>暴击率</t>
   </si>
   <si>
+    <t>暴击伤害</t>
+  </si>
+  <si>
     <t>形象icon</t>
   </si>
   <si>
@@ -115,13 +121,13 @@
     <t>0</t>
   </si>
   <si>
+    <t>2</t>
+  </si>
+  <si>
     <t>Adventurer1</t>
   </si>
   <si>
     <t>平平无奇之人</t>
-  </si>
-  <si>
-    <t>2</t>
   </si>
   <si>
     <t>大壮</t>
@@ -1206,7 +1212,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:L16"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="5.20833333333333" style="1" customWidth="1"/>
@@ -1215,15 +1221,15 @@
     <col min="4" max="4" width="6.08333333333333" style="1" customWidth="1"/>
     <col min="5" max="5" width="10.3166666666667" style="1" customWidth="1"/>
     <col min="6" max="6" width="9.00833333333333" style="1" customWidth="1"/>
-    <col min="7" max="7" width="12.0583333333333" style="1" customWidth="1"/>
-    <col min="8" max="8" width="11.7416666666667" style="2" customWidth="1"/>
-    <col min="9" max="9" width="12.7166666666667" style="1" customWidth="1"/>
-    <col min="10" max="10" width="14.3416666666667" style="1" customWidth="1"/>
-    <col min="11" max="11" width="34.75" style="1" customWidth="1"/>
-    <col min="12" max="16384" width="9" style="1"/>
+    <col min="7" max="8" width="12.0583333333333" style="1" customWidth="1"/>
+    <col min="9" max="9" width="11.7416666666667" style="2" customWidth="1"/>
+    <col min="10" max="10" width="12.7166666666667" style="1" customWidth="1"/>
+    <col min="11" max="11" width="14.3416666666667" style="1" customWidth="1"/>
+    <col min="12" max="12" width="34.75" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1245,424 +1251,469 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="E2" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="I2" s="2" t="s">
         <v>12</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>11</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>12</v>
       </c>
+      <c r="K2" s="2" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:12">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H3" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>20</v>
       </c>
+      <c r="I3" s="2" t="s">
+        <v>21</v>
+      </c>
       <c r="J3" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
-    <row r="5" customFormat="1" spans="1:11">
+    <row r="5" customFormat="1" spans="1:12">
       <c r="A5" s="1"/>
       <c r="B5" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="H5" s="1"/>
+        <v>29</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>30</v>
+      </c>
       <c r="I5" s="1"/>
-      <c r="J5" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="K5" s="1"/>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="L5" s="1"/>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:12">
       <c r="B6" s="1" t="s">
         <v>29</v>
       </c>
       <c r="C6" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I6" s="2">
+        <v>10001</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="B7" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H7" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F6" s="1" t="s">
+      <c r="I7" s="2">
+        <v>10002</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
+      <c r="B8" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I8" s="2">
+        <v>10003</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
+      <c r="B9" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I9" s="2">
+        <v>10004</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
+      <c r="B10" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I10" s="2">
+        <v>10005</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12">
+      <c r="B11" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="G6" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="H6" s="2">
-        <v>10001</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="J6" s="1" t="s">
+      <c r="E11" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I11" s="2">
+        <v>10006</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12">
+      <c r="B12" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I12" s="2">
+        <v>10007</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12">
+      <c r="B13" s="1" t="s">
         <v>34</v>
       </c>
+      <c r="C13" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I13" s="2">
+        <v>10008</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>60</v>
+      </c>
     </row>
-    <row r="7" spans="1:11">
-      <c r="B7" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="G7" s="1" t="s">
+    <row r="14" spans="1:12">
+      <c r="B14" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E14" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="H7" s="2">
-        <v>10002</v>
-      </c>
-      <c r="I7" s="1" t="s">
+      <c r="F14" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G14" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="J7" s="1" t="s">
-        <v>38</v>
+      <c r="H14" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I14" s="2">
+        <v>10009</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>62</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
-      <c r="B8" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F8" s="1" t="s">
+    <row r="15" spans="1:12">
+      <c r="B15" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C15" t="s">
+        <v>64</v>
+      </c>
+      <c r="D15" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="G8" s="1" t="s">
+      <c r="E15" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="H8" s="2">
-        <v>10003</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>43</v>
+      <c r="F15" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I15" s="2">
+        <v>10010</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>65</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
-      <c r="B9" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F9" s="1" t="s">
+    <row r="16" spans="1:12">
+      <c r="B16" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D16" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="G9" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="H9" s="2">
-        <v>10004</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="J9" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11">
-      <c r="B10" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="H10" s="2">
-        <v>10005</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="J10" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11">
-      <c r="B11" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G11" s="1" t="s">
+      <c r="E16" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="H11" s="2">
-        <v>10006</v>
-      </c>
-      <c r="I11" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="J11" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11">
-      <c r="B12" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="H12" s="2">
-        <v>10007</v>
-      </c>
-      <c r="I12" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="J12" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11">
-      <c r="B13" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="H13" s="2">
-        <v>10008</v>
-      </c>
-      <c r="I13" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="J13" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11">
-      <c r="B14" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="H14" s="2">
-        <v>10009</v>
-      </c>
-      <c r="I14" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="J14" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11">
-      <c r="B15" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C15" t="s">
-        <v>62</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="H15" s="2">
-        <v>10010</v>
-      </c>
-      <c r="I15" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="J15" s="1" t="s">
+      <c r="F16" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I16" s="2">
+        <v>10011</v>
+      </c>
+      <c r="J16" s="1" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="16" spans="1:11">
-      <c r="B16" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="H16" s="2">
-        <v>10011</v>
-      </c>
-      <c r="I16" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="J16" s="1" t="s">
-        <v>66</v>
+      <c r="K16" s="1" t="s">
+        <v>68</v>
       </c>
     </row>
   </sheetData>

--- a/Config/HeroConfig.xlsx
+++ b/Config/HeroConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="14850" windowHeight="9750"/>
+    <workbookView windowWidth="11535" windowHeight="9750"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="69">
   <si>
     <t>##var</t>
   </si>
@@ -79,6 +79,9 @@
     <t>float</t>
   </si>
   <si>
+    <t>int[]</t>
+  </si>
+  <si>
     <t>名字</t>
   </si>
   <si>
@@ -112,115 +115,112 @@
     <t>平凡之人</t>
   </si>
   <si>
-    <t>200</t>
+    <t>0</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>Adventurer1</t>
+  </si>
+  <si>
+    <t>平平无奇之人</t>
+  </si>
+  <si>
+    <t>大壮</t>
+  </si>
+  <si>
+    <t>Warrior1</t>
+  </si>
+  <si>
+    <t>受到的伤害-25%</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>狠人</t>
+  </si>
+  <si>
+    <t>0.05</t>
+  </si>
+  <si>
+    <t>10002|100021</t>
+  </si>
+  <si>
+    <t>造成的伤害+20%,且拥有15%暴击率</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>多面手</t>
+  </si>
+  <si>
+    <t>攻击时,对其他人造成25%的伤害</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>射手</t>
+  </si>
+  <si>
+    <t>Ranger1</t>
+  </si>
+  <si>
+    <t>攻击时,有25%概率额外攻击1次</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>大嗓门</t>
+  </si>
+  <si>
+    <t>Mage1</t>
+  </si>
+  <si>
+    <t>攻击时,对所有人造成30%的群体伤害</t>
   </si>
   <si>
     <t>7</t>
   </si>
   <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>Adventurer1</t>
-  </si>
-  <si>
-    <t>平平无奇之人</t>
-  </si>
-  <si>
-    <t>大壮</t>
-  </si>
-  <si>
-    <t>170</t>
+    <t>富豪</t>
+  </si>
+  <si>
+    <t>初始额外拥有30金币</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>武林高手</t>
+  </si>
+  <si>
+    <t>10007|100071</t>
+  </si>
+  <si>
+    <t>承受伤害时有20%概率免疫伤害,且拥有15%暴击率</t>
   </si>
   <si>
     <t>9</t>
   </si>
   <si>
-    <t>Warrior1</t>
-  </si>
-  <si>
-    <t>受到的伤害-20%</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>狠人</t>
-  </si>
-  <si>
-    <t>0.05</t>
-  </si>
-  <si>
-    <t>造成的伤害+10%,且拥有5%暴击率</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>多面手</t>
-  </si>
-  <si>
-    <t>160</t>
+    <t>赌神</t>
+  </si>
+  <si>
+    <t>额外拥有1次搓牌机会</t>
   </si>
   <si>
     <t>10</t>
   </si>
   <si>
-    <t>攻击时,对其他人造成30%的伤害</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>射手</t>
-  </si>
-  <si>
-    <t>Ranger1</t>
-  </si>
-  <si>
-    <t>攻击时,有50%概率额外攻击1次</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>大嗓门</t>
-  </si>
-  <si>
-    <t>Mage1</t>
-  </si>
-  <si>
-    <t>攻击时,对所有人造成50%的群体伤害</t>
-  </si>
-  <si>
-    <t>富豪</t>
-  </si>
-  <si>
-    <t>初始拥有20资金</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>武林高手</t>
-  </si>
-  <si>
-    <t>承受伤害时有25%概率免疫伤害,且初始拥有5%的暴击率</t>
-  </si>
-  <si>
-    <t>赌神</t>
-  </si>
-  <si>
-    <t>额外拥有1次搓牌的机会</t>
-  </si>
-  <si>
     <t>暴发户</t>
   </si>
   <si>
-    <t>商店里刷到史诗及以上品质的遗物概率提高5%</t>
+    <t>商店刷到史诗及以上品质的收藏品概率+15%</t>
   </si>
   <si>
     <t>11</t>
@@ -229,7 +229,7 @@
     <t>关系户</t>
   </si>
   <si>
-    <t>商店中的所有遗物的购买价格打八折</t>
+    <t>商店中的所有收藏品的购买价格-15%</t>
   </si>
   <si>
     <t>12</t>
@@ -238,7 +238,7 @@
     <t>经济教授</t>
   </si>
   <si>
-    <t>结算伤害后获得的金币数量+10%</t>
+    <t>每关通过后获得的金币数量+20%</t>
   </si>
 </sst>
 </file>
@@ -1219,10 +1219,11 @@
     <col min="2" max="2" width="4.01666666666667" style="1" customWidth="1"/>
     <col min="3" max="3" width="9" style="1"/>
     <col min="4" max="4" width="6.08333333333333" style="1" customWidth="1"/>
-    <col min="5" max="5" width="10.3166666666667" style="1" customWidth="1"/>
-    <col min="6" max="6" width="9.00833333333333" style="1" customWidth="1"/>
-    <col min="7" max="8" width="12.0583333333333" style="1" customWidth="1"/>
-    <col min="9" max="9" width="11.7416666666667" style="2" customWidth="1"/>
+    <col min="5" max="5" width="6.3" style="1" customWidth="1"/>
+    <col min="6" max="6" width="6.73333333333333" style="1" customWidth="1"/>
+    <col min="7" max="7" width="2.16666666666667" style="1" customWidth="1"/>
+    <col min="8" max="8" width="12.0583333333333" style="1" customWidth="1"/>
+    <col min="9" max="9" width="13.75" style="2" customWidth="1"/>
     <col min="10" max="10" width="12.7166666666667" style="1" customWidth="1"/>
     <col min="11" max="11" width="14.3416666666667" style="1" customWidth="1"/>
     <col min="12" max="12" width="34.75" style="1" customWidth="1"/>
@@ -1290,7 +1291,7 @@
         <v>13</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>12</v>
@@ -1307,346 +1308,346 @@
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" customFormat="1" spans="1:12">
       <c r="A5" s="1"/>
       <c r="B5" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D5" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="D5" s="2">
+        <v>200</v>
+      </c>
+      <c r="E5" s="2">
+        <v>7</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="G5" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="H5" s="1" t="s">
         <v>29</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>30</v>
       </c>
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
       <c r="K5" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L5" s="1"/>
     </row>
     <row r="6" spans="1:12">
       <c r="B6" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C6" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" s="2">
+        <v>180</v>
+      </c>
+      <c r="E6" s="2">
+        <v>7</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H6" s="1" t="s">
         <v>32</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>35</v>
       </c>
       <c r="I6" s="2">
         <v>10001</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="B7" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D7" s="2">
+        <v>200</v>
+      </c>
+      <c r="E7" s="2">
+        <v>5</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I7" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="J7" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="K7" s="1" t="s">
         <v>38</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="I7" s="2">
-        <v>10002</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="8" spans="1:12">
       <c r="B8" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>44</v>
+        <v>40</v>
+      </c>
+      <c r="D8" s="2">
+        <v>180</v>
+      </c>
+      <c r="E8" s="2">
+        <v>6</v>
       </c>
       <c r="F8" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G8" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="G8" s="1" t="s">
+      <c r="H8" s="1" t="s">
         <v>29</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>30</v>
       </c>
       <c r="I8" s="2">
         <v>10003</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9" spans="1:12">
       <c r="B9" s="1" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="D9" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="D9" s="2">
+        <v>180</v>
+      </c>
+      <c r="E9" s="2">
+        <v>6</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H9" s="1" t="s">
         <v>44</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>48</v>
       </c>
       <c r="I9" s="2">
         <v>10004</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10" spans="1:12">
       <c r="B10" s="1" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>44</v>
+        <v>47</v>
+      </c>
+      <c r="D10" s="2">
+        <v>180</v>
+      </c>
+      <c r="E10" s="2">
+        <v>5</v>
       </c>
       <c r="F10" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G10" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="G10" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="H10" s="1" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="I10" s="2">
         <v>10005</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11" spans="1:12">
       <c r="B11" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D11" s="2">
+        <v>180</v>
+      </c>
+      <c r="E11" s="2">
+        <v>6</v>
+      </c>
+      <c r="F11" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C11" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F11" s="1" t="s">
+      <c r="G11" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="G11" s="1" t="s">
+      <c r="H11" s="1" t="s">
         <v>29</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>30</v>
       </c>
       <c r="I11" s="2">
         <v>10006</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="12" spans="1:12">
       <c r="B12" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D12" s="2">
+        <v>170</v>
+      </c>
+      <c r="E12" s="2">
+        <v>6</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="K12" s="1" t="s">
         <v>56</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="I12" s="2">
-        <v>10007</v>
-      </c>
-      <c r="J12" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="K12" s="1" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="13" spans="1:12">
       <c r="B13" s="1" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E13" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D13" s="2">
+        <v>200</v>
+      </c>
+      <c r="E13" s="2">
+        <v>6</v>
+      </c>
+      <c r="F13" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F13" s="1" t="s">
+      <c r="G13" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="G13" s="1" t="s">
+      <c r="H13" s="1" t="s">
         <v>29</v>
-      </c>
-      <c r="H13" s="1" t="s">
-        <v>30</v>
       </c>
       <c r="I13" s="2">
         <v>10008</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14" spans="1:12">
       <c r="B14" s="1" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="D14" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E14" s="1" t="s">
+      <c r="D14" s="2">
+        <v>190</v>
+      </c>
+      <c r="E14" s="2">
+        <v>6</v>
+      </c>
+      <c r="F14" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F14" s="1" t="s">
+      <c r="G14" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="G14" s="1" t="s">
+      <c r="H14" s="1" t="s">
         <v>29</v>
-      </c>
-      <c r="H14" s="1" t="s">
-        <v>30</v>
       </c>
       <c r="I14" s="2">
         <v>10009</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="K14" s="1" t="s">
         <v>62</v>
@@ -1659,26 +1660,26 @@
       <c r="C15" t="s">
         <v>64</v>
       </c>
-      <c r="D15" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E15" s="1" t="s">
+      <c r="D15" s="2">
+        <v>190</v>
+      </c>
+      <c r="E15" s="2">
+        <v>6</v>
+      </c>
+      <c r="F15" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F15" s="1" t="s">
+      <c r="G15" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="G15" s="1" t="s">
+      <c r="H15" s="1" t="s">
         <v>29</v>
-      </c>
-      <c r="H15" s="1" t="s">
-        <v>30</v>
       </c>
       <c r="I15" s="2">
         <v>10010</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="K15" s="1" t="s">
         <v>65</v>
@@ -1691,20 +1692,20 @@
       <c r="C16" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="D16" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E16" s="1" t="s">
+      <c r="D16" s="2">
+        <v>190</v>
+      </c>
+      <c r="E16" s="2">
+        <v>6</v>
+      </c>
+      <c r="F16" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F16" s="1" t="s">
+      <c r="G16" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="G16" s="1" t="s">
+      <c r="H16" s="1" t="s">
         <v>29</v>
-      </c>
-      <c r="H16" s="1" t="s">
-        <v>30</v>
       </c>
       <c r="I16" s="2">
         <v>10011</v>

--- a/Config/HeroConfig.xlsx
+++ b/Config/HeroConfig.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\cardclient\Config\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitWork\cardclient\Config\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="11535" windowHeight="9750"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="11535" windowHeight="9750"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="73">
   <si>
     <t>##var</t>
   </si>
@@ -121,18 +121,12 @@
     <t>2</t>
   </si>
   <si>
-    <t>Adventurer1</t>
-  </si>
-  <si>
     <t>平平无奇之人</t>
   </si>
   <si>
     <t>大壮</t>
   </si>
   <si>
-    <t>Warrior1</t>
-  </si>
-  <si>
     <t>受到的伤害-25%</t>
   </si>
   <si>
@@ -166,9 +160,6 @@
     <t>射手</t>
   </si>
   <si>
-    <t>Ranger1</t>
-  </si>
-  <si>
     <t>攻击时,有25%概率额外攻击1次</t>
   </si>
   <si>
@@ -178,9 +169,6 @@
     <t>大嗓门</t>
   </si>
   <si>
-    <t>Mage1</t>
-  </si>
-  <si>
     <t>攻击时,对所有人造成30%的群体伤害</t>
   </si>
   <si>
@@ -239,19 +227,45 @@
   </si>
   <si>
     <t>每关通过后获得的金币数量+20%</t>
+  </si>
+  <si>
+    <t>Adventurer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Warrior</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Adventurer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Adventurer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ranger</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mage</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Adventurer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Adventurer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="20">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -260,345 +274,29 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -606,255 +304,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -864,62 +320,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1206,31 +621,31 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L16"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="5.20833333333333" style="1" customWidth="1"/>
-    <col min="2" max="2" width="4.01666666666667" style="1" customWidth="1"/>
+    <col min="1" max="1" width="5.25" style="1" customWidth="1"/>
+    <col min="2" max="2" width="4" style="1" customWidth="1"/>
     <col min="3" max="3" width="9" style="1"/>
-    <col min="4" max="4" width="6.08333333333333" style="1" customWidth="1"/>
-    <col min="5" max="5" width="6.3" style="1" customWidth="1"/>
-    <col min="6" max="6" width="6.73333333333333" style="1" customWidth="1"/>
-    <col min="7" max="7" width="2.16666666666667" style="1" customWidth="1"/>
-    <col min="8" max="8" width="12.0583333333333" style="1" customWidth="1"/>
+    <col min="4" max="4" width="6.125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="6.25" style="1" customWidth="1"/>
+    <col min="6" max="6" width="6.75" style="1" customWidth="1"/>
+    <col min="7" max="7" width="2.125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="12" style="1" customWidth="1"/>
     <col min="9" max="9" width="13.75" style="2" customWidth="1"/>
-    <col min="10" max="10" width="12.7166666666667" style="1" customWidth="1"/>
-    <col min="11" max="11" width="14.3416666666667" style="1" customWidth="1"/>
+    <col min="10" max="10" width="12.75" style="1" customWidth="1"/>
+    <col min="11" max="11" width="14.375" style="1" customWidth="1"/>
     <col min="12" max="12" width="34.75" style="1" customWidth="1"/>
     <col min="13" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1265,7 +680,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
@@ -1300,7 +715,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:12">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
@@ -1335,7 +750,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" customFormat="1" spans="1:12">
+    <row r="5" spans="1:12" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A5" s="1"/>
       <c r="B5" s="1" t="s">
         <v>25</v>
@@ -1356,21 +771,21 @@
         <v>28</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>29</v>
+        <v>65</v>
       </c>
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
       <c r="K5" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="L5" s="1"/>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="B6" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="L5" s="1"/>
-    </row>
-    <row r="6" spans="1:12">
-      <c r="B6" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>31</v>
       </c>
       <c r="D6" s="2">
         <v>180</v>
@@ -1385,7 +800,7 @@
         <v>28</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>32</v>
+        <v>66</v>
       </c>
       <c r="I6" s="2">
         <v>10001</v>
@@ -1394,15 +809,15 @@
         <v>25</v>
       </c>
       <c r="K6" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="B7" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>33</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12">
-      <c r="B7" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>35</v>
       </c>
       <c r="D7" s="2">
         <v>200</v>
@@ -1411,30 +826,30 @@
         <v>5</v>
       </c>
       <c r="F7" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="K7" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="G7" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="I7" s="2" t="s">
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="B8" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="J7" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="K7" s="1" t="s">
+      <c r="C8" s="1" t="s">
         <v>38</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12">
-      <c r="B8" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>40</v>
       </c>
       <c r="D8" s="2">
         <v>180</v>
@@ -1448,25 +863,25 @@
       <c r="G8" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="H8" s="1" t="s">
-        <v>29</v>
+      <c r="H8" s="3" t="s">
+        <v>68</v>
       </c>
       <c r="I8" s="2">
         <v>10003</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="K8" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="B9" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>41</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12">
-      <c r="B9" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>43</v>
       </c>
       <c r="D9" s="2">
         <v>180</v>
@@ -1480,25 +895,25 @@
       <c r="G9" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="H9" s="1" t="s">
-        <v>44</v>
+      <c r="H9" s="3" t="s">
+        <v>69</v>
       </c>
       <c r="I9" s="2">
         <v>10004</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.15">
       <c r="B10" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D10" s="2">
         <v>180</v>
@@ -1512,25 +927,25 @@
       <c r="G10" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="H10" s="1" t="s">
-        <v>48</v>
+      <c r="H10" s="3" t="s">
+        <v>70</v>
       </c>
       <c r="I10" s="2">
         <v>10005</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.15">
       <c r="B11" s="1" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D11" s="2">
         <v>180</v>
@@ -1544,25 +959,25 @@
       <c r="G11" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="H11" s="1" t="s">
-        <v>29</v>
+      <c r="H11" s="3" t="s">
+        <v>71</v>
       </c>
       <c r="I11" s="2">
         <v>10006</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.15">
       <c r="B12" s="1" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D12" s="2">
         <v>170</v>
@@ -1571,30 +986,30 @@
         <v>6</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="H12" s="1" t="s">
-        <v>29</v>
+      <c r="H12" s="3" t="s">
+        <v>67</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.15">
       <c r="B13" s="1" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D13" s="2">
         <v>200</v>
@@ -1608,25 +1023,25 @@
       <c r="G13" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="H13" s="1" t="s">
-        <v>29</v>
+      <c r="H13" s="3" t="s">
+        <v>72</v>
       </c>
       <c r="I13" s="2">
         <v>10008</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.15">
       <c r="B14" s="1" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D14" s="2">
         <v>190</v>
@@ -1640,25 +1055,25 @@
       <c r="G14" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="H14" s="1" t="s">
-        <v>29</v>
+      <c r="H14" s="3" t="s">
+        <v>71</v>
       </c>
       <c r="I14" s="2">
         <v>10009</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.15">
       <c r="B15" s="1" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C15" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D15" s="2">
         <v>190</v>
@@ -1672,25 +1087,25 @@
       <c r="G15" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="H15" s="1" t="s">
-        <v>29</v>
+      <c r="H15" s="3" t="s">
+        <v>67</v>
       </c>
       <c r="I15" s="2">
         <v>10010</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.15">
       <c r="B16" s="1" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D16" s="2">
         <v>190</v>
@@ -1704,22 +1119,22 @@
       <c r="G16" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="H16" s="1" t="s">
-        <v>29</v>
+      <c r="H16" s="3" t="s">
+        <v>71</v>
       </c>
       <c r="I16" s="2">
         <v>10011</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Config/HeroConfig.xlsx
+++ b/Config/HeroConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="17820" windowHeight="11520"/>
+    <workbookView windowWidth="14445" windowHeight="11505"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -251,14 +251,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -731,133 +724,133 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -871,7 +864,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1222,7 +1215,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L16"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="5.25" style="1" customWidth="1"/>
@@ -1234,13 +1227,14 @@
     <col min="7" max="7" width="2.125" style="1" customWidth="1"/>
     <col min="8" max="8" width="12" style="1" customWidth="1"/>
     <col min="9" max="9" width="13.75" style="2" customWidth="1"/>
-    <col min="10" max="11" width="12.75" style="1" customWidth="1"/>
-    <col min="12" max="12" width="14.375" style="1" customWidth="1"/>
-    <col min="13" max="13" width="34.75" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="9" style="1" customWidth="1"/>
+    <col min="10" max="10" width="12.75" style="1" customWidth="1"/>
+    <col min="11" max="11" width="14.375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="34.75" style="1" customWidth="1"/>
+    <col min="13" max="16383" width="9" style="1" customWidth="1"/>
+    <col min="16384" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1268,14 +1262,14 @@
       <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
       <c r="K1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="L1" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:11">
       <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
@@ -1303,15 +1297,14 @@
       <c r="I2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="J2" s="2"/>
+      <c r="J2" s="2" t="s">
+        <v>12</v>
+      </c>
       <c r="K2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="L2" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:12">
+    <row r="3" spans="1:11">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
@@ -1339,14 +1332,14 @@
       <c r="I3" s="2" t="s">
         <v>22</v>
       </c>
+      <c r="J3" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="K3" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="L3" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:12">
+    <row r="5" spans="1:11">
       <c r="B5" s="1" t="s">
         <v>25</v>
       </c>
@@ -1369,11 +1362,11 @@
         <v>29</v>
       </c>
       <c r="I5" s="1"/>
-      <c r="L5" s="1" t="s">
+      <c r="K5" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:12">
+    <row r="6" spans="1:11">
       <c r="B6" s="1" t="s">
         <v>28</v>
       </c>
@@ -1398,14 +1391,14 @@
       <c r="I6" s="2">
         <v>10001</v>
       </c>
+      <c r="J6" s="1" t="s">
+        <v>25</v>
+      </c>
       <c r="K6" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="L6" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:12">
+    <row r="7" spans="1:11">
       <c r="B7" s="1" t="s">
         <v>34</v>
       </c>
@@ -1430,14 +1423,14 @@
       <c r="I7" s="2" t="s">
         <v>37</v>
       </c>
+      <c r="J7" s="1" t="s">
+        <v>28</v>
+      </c>
       <c r="K7" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="L7" s="1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:12">
+    <row r="8" spans="1:11">
       <c r="B8" s="1" t="s">
         <v>39</v>
       </c>
@@ -1462,14 +1455,14 @@
       <c r="I8" s="2">
         <v>10003</v>
       </c>
+      <c r="J8" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="K8" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="L8" s="1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="9" spans="1:12">
+    <row r="9" spans="1:11">
       <c r="B9" s="1" t="s">
         <v>42</v>
       </c>
@@ -1494,14 +1487,14 @@
       <c r="I9" s="2">
         <v>10004</v>
       </c>
+      <c r="J9" s="1" t="s">
+        <v>39</v>
+      </c>
       <c r="K9" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="L9" s="1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="10" spans="1:12">
+    <row r="10" spans="1:11">
       <c r="B10" s="1" t="s">
         <v>46</v>
       </c>
@@ -1526,14 +1519,14 @@
       <c r="I10" s="2">
         <v>10005</v>
       </c>
+      <c r="J10" s="1" t="s">
+        <v>42</v>
+      </c>
       <c r="K10" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="L10" s="1" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="11" spans="1:12">
+    <row r="11" spans="1:11">
       <c r="B11" s="1" t="s">
         <v>50</v>
       </c>
@@ -1558,14 +1551,14 @@
       <c r="I11" s="2">
         <v>10006</v>
       </c>
+      <c r="J11" s="1" t="s">
+        <v>46</v>
+      </c>
       <c r="K11" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="L11" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="12" spans="1:12">
+    <row r="12" spans="1:11">
       <c r="B12" s="1" t="s">
         <v>53</v>
       </c>
@@ -1590,14 +1583,14 @@
       <c r="I12" s="2" t="s">
         <v>55</v>
       </c>
+      <c r="J12" s="1" t="s">
+        <v>50</v>
+      </c>
       <c r="K12" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="L12" s="1" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="13" spans="1:12">
+    <row r="13" spans="1:11">
       <c r="B13" s="1" t="s">
         <v>57</v>
       </c>
@@ -1622,14 +1615,14 @@
       <c r="I13" s="2">
         <v>10008</v>
       </c>
+      <c r="J13" s="1" t="s">
+        <v>53</v>
+      </c>
       <c r="K13" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="L13" s="1" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="14" spans="1:12">
+    <row r="14" spans="1:11">
       <c r="B14" s="1" t="s">
         <v>60</v>
       </c>
@@ -1654,14 +1647,14 @@
       <c r="I14" s="2">
         <v>10009</v>
       </c>
+      <c r="J14" s="1" t="s">
+        <v>57</v>
+      </c>
       <c r="K14" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="L14" s="1" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="15" spans="1:12">
+    <row r="15" spans="1:11">
       <c r="B15" s="1" t="s">
         <v>63</v>
       </c>
@@ -1686,14 +1679,14 @@
       <c r="I15" s="2">
         <v>10010</v>
       </c>
+      <c r="J15" s="1" t="s">
+        <v>60</v>
+      </c>
       <c r="K15" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="L15" s="1" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="16" spans="1:12">
+    <row r="16" spans="1:11">
       <c r="B16" s="1" t="s">
         <v>66</v>
       </c>
@@ -1718,10 +1711,10 @@
       <c r="I16" s="2">
         <v>10011</v>
       </c>
+      <c r="J16" s="1" t="s">
+        <v>63</v>
+      </c>
       <c r="K16" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="L16" s="1" t="s">
         <v>68</v>
       </c>
     </row>

--- a/Config/HeroConfig.xlsx
+++ b/Config/HeroConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="14445" windowHeight="11505"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -220,7 +220,7 @@
     <t>暴发户</t>
   </si>
   <si>
-    <t>商店刷到史诗及以上品质的收藏品概率+15%</t>
+    <t>商店刷到史诗及以上品质的圣物概率+15%</t>
   </si>
   <si>
     <t>11</t>
@@ -229,7 +229,7 @@
     <t>关系户</t>
   </si>
   <si>
-    <t>商店中的所有收藏品的购买价格-15%</t>
+    <t>商店中的所有圣物的购买价格-15%</t>
   </si>
   <si>
     <t>12</t>

--- a/Config/HeroConfig.xlsx
+++ b/Config/HeroConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="17640" windowHeight="12240"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -181,7 +181,7 @@
     <t>6</t>
   </si>
   <si>
-    <t>大嗓门</t>
+    <t>灰烬术士</t>
   </si>
   <si>
     <t>People6</t>

--- a/Config/HeroConfig.xlsx
+++ b/Config/HeroConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="15285" windowHeight="12825"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="127">
   <si>
     <t>##var</t>
   </si>
@@ -208,13 +208,13 @@
     <t>武林高手</t>
   </si>
   <si>
+    <t>0.15</t>
+  </si>
+  <si>
     <t>People8</t>
   </si>
   <si>
-    <t>10007|100071</t>
-  </si>
-  <si>
-    <t>承受伤害时有25%概率免疫伤害,且拥有15%暴击率</t>
+    <t>初始拥有15%暴击率,25%闪避率</t>
   </si>
   <si>
     <t>9</t>
@@ -226,7 +226,7 @@
     <t>People9</t>
   </si>
   <si>
-    <t>每关[搓牌]使用次数+2</t>
+    <t>每关[搓牌]使用次数+1</t>
   </si>
   <si>
     <t>10</t>
@@ -238,7 +238,7 @@
     <t>People10</t>
   </si>
   <si>
-    <t>商店刷到史诗及以上品质的圣物概率+25%</t>
+    <t>商店刷到史诗及以上品质的圣物概率+10%</t>
   </si>
   <si>
     <t>11</t>
@@ -286,7 +286,7 @@
     <t>People14</t>
   </si>
   <si>
-    <t>对血量小于10%的非领主敌人造成伤害时,有20%概率直接斩杀</t>
+    <t>攻击血量小于10%的非领主敌人时,有20%概率直接斩杀</t>
   </si>
   <si>
     <t>15</t>
@@ -310,7 +310,7 @@
     <t>People16</t>
   </si>
   <si>
-    <t>圣物携带上限+2</t>
+    <t>圣物携带上限+1</t>
   </si>
   <si>
     <t>17</t>
@@ -334,7 +334,7 @@
     <t>People18</t>
   </si>
   <si>
-    <t>每次通关后额外回复自身10%血量</t>
+    <t>每回合开始时回复自身2%血量</t>
   </si>
   <si>
     <t>19</t>
@@ -394,7 +394,7 @@
     <t>People23</t>
   </si>
   <si>
-    <t>每关第一轮比牌时,结算时的倍率+2</t>
+    <t>每关首回合比牌时,结算时的倍率+5</t>
   </si>
   <si>
     <t>24</t>
@@ -578,12 +578,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -904,7 +910,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
@@ -928,16 +934,16 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="6">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
@@ -946,96 +952,108 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1389,403 +1407,403 @@
   <dimension ref="A1:K28"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="3.075" style="1" customWidth="1"/>
-    <col min="2" max="2" width="4" style="1" customWidth="1"/>
+    <col min="1" max="1" width="3.075" style="2" customWidth="1"/>
+    <col min="2" max="2" width="4" style="2" customWidth="1"/>
     <col min="3" max="3" width="9" customWidth="1"/>
-    <col min="4" max="4" width="6.125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="6.25" style="1" customWidth="1"/>
-    <col min="6" max="6" width="6.35" style="1" customWidth="1"/>
-    <col min="7" max="7" width="7.88333333333333" style="1" customWidth="1"/>
-    <col min="8" max="8" width="12" style="1" customWidth="1"/>
-    <col min="9" max="9" width="13.75" style="2" customWidth="1"/>
-    <col min="10" max="10" width="4.41666666666667" style="1" customWidth="1"/>
-    <col min="11" max="11" width="14.375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="34.75" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="9" style="1" customWidth="1"/>
+    <col min="4" max="4" width="6.125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="6.25" style="2" customWidth="1"/>
+    <col min="6" max="6" width="6.35" style="2" customWidth="1"/>
+    <col min="7" max="7" width="7.88333333333333" style="2" customWidth="1"/>
+    <col min="8" max="8" width="12" style="2" customWidth="1"/>
+    <col min="9" max="9" width="13.75" style="3" customWidth="1"/>
+    <col min="10" max="10" width="4.41666666666667" style="2" customWidth="1"/>
+    <col min="11" max="11" width="14.375" style="2" customWidth="1"/>
+    <col min="12" max="12" width="34.75" style="2" customWidth="1"/>
+    <col min="13" max="16384" width="9" style="2" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:11">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C2" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="K2" s="3" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:11">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C3" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="H3" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="J3" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="K3" s="2" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:11">
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="2" t="s">
         <v>25</v>
       </c>
       <c r="C5" t="s">
         <v>26</v>
       </c>
-      <c r="D5" s="2">
+      <c r="D5" s="3">
         <v>320</v>
       </c>
-      <c r="E5" s="2">
+      <c r="E5" s="3">
         <v>40</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="F5" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="G5" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="H5" s="1" t="s">
+      <c r="G5" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="I5" s="1"/>
-      <c r="K5" s="1" t="s">
+      <c r="I5" s="2"/>
+      <c r="K5" s="2" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:11">
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C6" t="s">
         <v>31</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D6" s="3">
         <v>300</v>
       </c>
-      <c r="E6" s="2">
-        <v>34</v>
-      </c>
-      <c r="F6" s="1" t="s">
+      <c r="E6" s="3">
+        <v>34</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="G6" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="H6" s="1" t="s">
+      <c r="G6" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H6" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="I6" s="2">
+      <c r="I6" s="3">
         <v>10001</v>
       </c>
-      <c r="J6" s="1" t="s">
+      <c r="J6" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="K6" s="1" t="s">
+      <c r="K6" s="2" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:11">
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="2" t="s">
         <v>34</v>
       </c>
       <c r="C7" t="s">
         <v>35</v>
       </c>
-      <c r="D7" s="2">
+      <c r="D7" s="3">
         <v>320</v>
       </c>
-      <c r="E7" s="2">
-        <v>34</v>
-      </c>
-      <c r="F7" s="1" t="s">
+      <c r="E7" s="3">
+        <v>34</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="G7" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="H7" s="1" t="s">
+      <c r="G7" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H7" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="I7" s="2" t="s">
+      <c r="I7" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="J7" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="K7" s="1" t="s">
+      <c r="J7" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="K7" s="2" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="8" spans="1:11">
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="2" t="s">
         <v>40</v>
       </c>
       <c r="C8" t="s">
         <v>41</v>
       </c>
-      <c r="D8" s="2">
+      <c r="D8" s="3">
         <v>320</v>
       </c>
-      <c r="E8" s="2">
-        <v>34</v>
-      </c>
-      <c r="F8" s="1" t="s">
+      <c r="E8" s="3">
+        <v>34</v>
+      </c>
+      <c r="F8" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="G8" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="H8" s="1" t="s">
+      <c r="G8" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H8" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="I8" s="2">
+      <c r="I8" s="3">
         <v>10003</v>
       </c>
-      <c r="J8" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K8" s="1" t="s">
+      <c r="J8" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="K8" s="2" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="9" spans="1:11">
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="2" t="s">
         <v>44</v>
       </c>
       <c r="C9" t="s">
         <v>45</v>
       </c>
-      <c r="D9" s="2">
+      <c r="D9" s="3">
         <v>320</v>
       </c>
-      <c r="E9" s="2">
-        <v>34</v>
-      </c>
-      <c r="F9" s="1" t="s">
+      <c r="E9" s="3">
+        <v>34</v>
+      </c>
+      <c r="F9" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="G9" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="H9" s="1" t="s">
+      <c r="G9" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H9" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="I9" s="2">
+      <c r="I9" s="3">
         <v>10004</v>
       </c>
-      <c r="J9" s="1" t="s">
+      <c r="J9" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="K9" s="1" t="s">
+      <c r="K9" s="2" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="10" spans="1:11">
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="2" t="s">
         <v>48</v>
       </c>
       <c r="C10" t="s">
         <v>49</v>
       </c>
-      <c r="D10" s="2">
+      <c r="D10" s="3">
         <v>320</v>
       </c>
-      <c r="E10" s="2">
-        <v>34</v>
-      </c>
-      <c r="F10" s="1" t="s">
+      <c r="E10" s="3">
+        <v>34</v>
+      </c>
+      <c r="F10" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="G10" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="H10" s="1" t="s">
+      <c r="G10" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H10" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="I10" s="2">
+      <c r="I10" s="3">
         <v>10005</v>
       </c>
-      <c r="J10" s="1" t="s">
+      <c r="J10" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="K10" s="1" t="s">
+      <c r="K10" s="2" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="11" spans="1:11">
-      <c r="B11" s="1" t="s">
+      <c r="B11" s="2" t="s">
         <v>52</v>
       </c>
       <c r="C11" t="s">
         <v>53</v>
       </c>
-      <c r="D11" s="2">
+      <c r="D11" s="3">
         <v>330</v>
       </c>
-      <c r="E11" s="2">
-        <v>34</v>
-      </c>
-      <c r="F11" s="1" t="s">
+      <c r="E11" s="3">
+        <v>34</v>
+      </c>
+      <c r="F11" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="G11" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="H11" s="1" t="s">
+      <c r="G11" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H11" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="I11" s="2">
+      <c r="I11" s="3">
         <v>10006</v>
       </c>
-      <c r="J11" s="1" t="s">
+      <c r="J11" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="K11" s="1" t="s">
+      <c r="K11" s="2" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="12" spans="1:11">
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="2" t="s">
         <v>56</v>
       </c>
       <c r="C12" t="s">
         <v>57</v>
       </c>
-      <c r="D12" s="2">
+      <c r="D12" s="3">
         <v>320</v>
       </c>
-      <c r="E12" s="2">
-        <v>34</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="H12" s="1" t="s">
+      <c r="E12" s="3">
+        <v>34</v>
+      </c>
+      <c r="F12" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="I12" s="2" t="s">
+      <c r="G12" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H12" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="J12" s="1" t="s">
+      <c r="I12" s="3">
+        <v>10007</v>
+      </c>
+      <c r="J12" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="K12" s="1" t="s">
+      <c r="K12" s="4" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="13" spans="1:11">
-      <c r="B13" s="1" t="s">
+      <c r="B13" s="2" t="s">
         <v>61</v>
       </c>
       <c r="C13" t="s">
         <v>62</v>
       </c>
-      <c r="D13" s="2">
+      <c r="D13" s="3">
         <v>340</v>
       </c>
-      <c r="E13" s="2">
-        <v>34</v>
-      </c>
-      <c r="F13" s="1" t="s">
+      <c r="E13" s="3">
+        <v>34</v>
+      </c>
+      <c r="F13" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="G13" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="H13" s="1" t="s">
+      <c r="G13" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H13" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="I13" s="2">
+      <c r="I13" s="3">
         <v>10008</v>
       </c>
-      <c r="J13" s="1" t="s">
+      <c r="J13" s="2" t="s">
         <v>56</v>
       </c>
       <c r="K13" t="s">
@@ -1793,95 +1811,95 @@
       </c>
     </row>
     <row r="14" spans="1:11">
-      <c r="B14" s="1" t="s">
+      <c r="B14" s="2" t="s">
         <v>65</v>
       </c>
       <c r="C14" t="s">
         <v>66</v>
       </c>
-      <c r="D14" s="2">
+      <c r="D14" s="3">
         <v>330</v>
       </c>
-      <c r="E14" s="2">
-        <v>34</v>
-      </c>
-      <c r="F14" s="1" t="s">
+      <c r="E14" s="3">
+        <v>34</v>
+      </c>
+      <c r="F14" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="G14" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="H14" s="1" t="s">
+      <c r="G14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H14" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="I14" s="2">
+      <c r="I14" s="3">
         <v>10009</v>
       </c>
-      <c r="J14" s="1" t="s">
+      <c r="J14" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="K14" s="1" t="s">
+      <c r="K14" s="2" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="15" spans="1:11">
-      <c r="B15" s="1" t="s">
+      <c r="B15" s="2" t="s">
         <v>69</v>
       </c>
       <c r="C15" t="s">
         <v>70</v>
       </c>
-      <c r="D15" s="2">
+      <c r="D15" s="3">
         <v>330</v>
       </c>
-      <c r="E15" s="2">
-        <v>34</v>
-      </c>
-      <c r="F15" s="1" t="s">
+      <c r="E15" s="3">
+        <v>34</v>
+      </c>
+      <c r="F15" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="G15" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="H15" s="1" t="s">
+      <c r="G15" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H15" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="I15" s="2">
+      <c r="I15" s="3">
         <v>10010</v>
       </c>
-      <c r="J15" s="1" t="s">
+      <c r="J15" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="K15" s="1" t="s">
+      <c r="K15" s="2" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="16" spans="1:11">
-      <c r="B16" s="1" t="s">
+      <c r="B16" s="2" t="s">
         <v>73</v>
       </c>
       <c r="C16" t="s">
         <v>74</v>
       </c>
-      <c r="D16" s="2">
+      <c r="D16" s="3">
         <v>340</v>
       </c>
-      <c r="E16" s="2">
-        <v>34</v>
-      </c>
-      <c r="F16" s="1" t="s">
+      <c r="E16" s="3">
+        <v>34</v>
+      </c>
+      <c r="F16" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="G16" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="H16" s="1" t="s">
+      <c r="G16" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H16" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="I16" s="2">
+      <c r="I16" s="3">
         <v>10011</v>
       </c>
-      <c r="J16" s="1" t="s">
+      <c r="J16" s="2" t="s">
         <v>69</v>
       </c>
       <c r="K16" t="s">
@@ -1889,31 +1907,31 @@
       </c>
     </row>
     <row r="17" spans="2:11">
-      <c r="B17" s="1" t="s">
+      <c r="B17" s="2" t="s">
         <v>77</v>
       </c>
       <c r="C17" t="s">
         <v>78</v>
       </c>
-      <c r="D17" s="2">
+      <c r="D17" s="3">
         <v>300</v>
       </c>
-      <c r="E17" s="2">
-        <v>34</v>
-      </c>
-      <c r="F17" s="1" t="s">
+      <c r="E17" s="3">
+        <v>34</v>
+      </c>
+      <c r="F17" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="G17" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="H17" s="1" t="s">
+      <c r="G17" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H17" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="I17" s="2">
+      <c r="I17" s="3">
         <v>10012</v>
       </c>
-      <c r="J17" s="1" t="s">
+      <c r="J17" s="2" t="s">
         <v>73</v>
       </c>
       <c r="K17" t="s">
@@ -1921,31 +1939,31 @@
       </c>
     </row>
     <row r="18" spans="2:11">
-      <c r="B18" s="1" t="s">
+      <c r="B18" s="2" t="s">
         <v>81</v>
       </c>
       <c r="C18" t="s">
         <v>82</v>
       </c>
-      <c r="D18" s="2">
+      <c r="D18" s="3">
         <v>320</v>
       </c>
-      <c r="E18" s="2">
-        <v>34</v>
-      </c>
-      <c r="F18" s="1" t="s">
+      <c r="E18" s="3">
+        <v>34</v>
+      </c>
+      <c r="F18" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="G18" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="H18" s="1" t="s">
+      <c r="G18" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H18" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="I18" s="2">
+      <c r="I18" s="3">
         <v>10013</v>
       </c>
-      <c r="J18" s="1" t="s">
+      <c r="J18" s="2" t="s">
         <v>77</v>
       </c>
       <c r="K18" t="s">
@@ -1953,31 +1971,31 @@
       </c>
     </row>
     <row r="19" spans="2:11">
-      <c r="B19" s="1" t="s">
+      <c r="B19" s="2" t="s">
         <v>85</v>
       </c>
       <c r="C19" t="s">
         <v>86</v>
       </c>
-      <c r="D19" s="2">
+      <c r="D19" s="3">
         <v>320</v>
       </c>
-      <c r="E19" s="2">
-        <v>34</v>
-      </c>
-      <c r="F19" s="1" t="s">
+      <c r="E19" s="3">
+        <v>34</v>
+      </c>
+      <c r="F19" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="G19" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="H19" s="1" t="s">
+      <c r="G19" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H19" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="I19" s="2">
+      <c r="I19" s="3">
         <v>10014</v>
       </c>
-      <c r="J19" s="1" t="s">
+      <c r="J19" s="2" t="s">
         <v>81</v>
       </c>
       <c r="K19" t="s">
@@ -1985,31 +2003,31 @@
       </c>
     </row>
     <row r="20" spans="2:11">
-      <c r="B20" s="1" t="s">
+      <c r="B20" s="2" t="s">
         <v>89</v>
       </c>
       <c r="C20" t="s">
         <v>90</v>
       </c>
-      <c r="D20" s="2">
+      <c r="D20" s="3">
         <v>300</v>
       </c>
-      <c r="E20" s="2">
-        <v>34</v>
-      </c>
-      <c r="F20" s="1" t="s">
+      <c r="E20" s="3">
+        <v>34</v>
+      </c>
+      <c r="F20" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="G20" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="H20" s="1" t="s">
+      <c r="G20" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H20" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="I20" s="2">
+      <c r="I20" s="3">
         <v>10015</v>
       </c>
-      <c r="J20" s="1" t="s">
+      <c r="J20" s="2" t="s">
         <v>85</v>
       </c>
       <c r="K20" t="s">
@@ -2017,48 +2035,48 @@
       </c>
     </row>
     <row r="21" spans="2:11">
-      <c r="B21" s="1" t="s">
+      <c r="B21" s="2" t="s">
         <v>93</v>
       </c>
       <c r="C21" t="s">
         <v>94</v>
       </c>
-      <c r="D21" s="2">
+      <c r="D21" s="3">
         <v>330</v>
       </c>
-      <c r="E21" s="2">
-        <v>34</v>
-      </c>
-      <c r="F21" s="1" t="s">
+      <c r="E21" s="3">
+        <v>34</v>
+      </c>
+      <c r="F21" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="G21" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="H21" s="1" t="s">
+      <c r="G21" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H21" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="I21" s="2">
+      <c r="I21" s="3">
         <v>10016</v>
       </c>
-      <c r="J21" s="1" t="s">
+      <c r="J21" s="2" t="s">
         <v>89</v>
       </c>
       <c r="K21" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="22" spans="2:11">
+    <row r="22" s="1" customFormat="1" spans="2:11">
       <c r="B22" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C22" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="D22" s="2">
+      <c r="D22" s="6">
         <v>320</v>
       </c>
-      <c r="E22" s="2">
+      <c r="E22" s="6">
         <v>34</v>
       </c>
       <c r="F22" s="1" t="s">
@@ -2070,42 +2088,42 @@
       <c r="H22" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="I22" s="2">
+      <c r="I22" s="6">
         <v>10017</v>
       </c>
       <c r="J22" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="K22" t="s">
+      <c r="K22" s="5" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="23" spans="2:11">
-      <c r="B23" s="1" t="s">
+      <c r="B23" s="2" t="s">
         <v>101</v>
       </c>
       <c r="C23" t="s">
         <v>102</v>
       </c>
-      <c r="D23" s="2">
+      <c r="D23" s="3">
         <v>330</v>
       </c>
-      <c r="E23" s="2">
-        <v>34</v>
-      </c>
-      <c r="F23" s="1" t="s">
+      <c r="E23" s="3">
+        <v>34</v>
+      </c>
+      <c r="F23" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="G23" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="H23" s="1" t="s">
+      <c r="G23" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H23" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="I23" s="2">
+      <c r="I23" s="3">
         <v>10018</v>
       </c>
-      <c r="J23" s="1" t="s">
+      <c r="J23" s="2" t="s">
         <v>97</v>
       </c>
       <c r="K23" t="s">
@@ -2113,31 +2131,31 @@
       </c>
     </row>
     <row r="24" spans="2:11">
-      <c r="B24" s="1" t="s">
+      <c r="B24" s="2" t="s">
         <v>105</v>
       </c>
       <c r="C24" t="s">
         <v>106</v>
       </c>
-      <c r="D24" s="2">
+      <c r="D24" s="3">
         <v>300</v>
       </c>
-      <c r="E24" s="2">
-        <v>34</v>
-      </c>
-      <c r="F24" s="1" t="s">
+      <c r="E24" s="3">
+        <v>34</v>
+      </c>
+      <c r="F24" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="G24" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="H24" s="1" t="s">
+      <c r="G24" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H24" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="I24" s="2">
+      <c r="I24" s="3">
         <v>10019</v>
       </c>
-      <c r="J24" s="1" t="s">
+      <c r="J24" s="2" t="s">
         <v>101</v>
       </c>
       <c r="K24" t="s">
@@ -2145,31 +2163,31 @@
       </c>
     </row>
     <row r="25" spans="2:11">
-      <c r="B25" s="1" t="s">
+      <c r="B25" s="2" t="s">
         <v>109</v>
       </c>
       <c r="C25" t="s">
         <v>110</v>
       </c>
-      <c r="D25" s="2">
+      <c r="D25" s="3">
         <v>310</v>
       </c>
-      <c r="E25" s="2">
-        <v>34</v>
-      </c>
-      <c r="F25" s="1" t="s">
+      <c r="E25" s="3">
+        <v>34</v>
+      </c>
+      <c r="F25" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="G25" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="H25" s="1" t="s">
+      <c r="G25" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H25" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="I25" s="2">
+      <c r="I25" s="3">
         <v>10020</v>
       </c>
-      <c r="J25" s="1" t="s">
+      <c r="J25" s="2" t="s">
         <v>105</v>
       </c>
       <c r="K25" t="s">
@@ -2177,31 +2195,31 @@
       </c>
     </row>
     <row r="26" spans="2:11">
-      <c r="B26" s="1" t="s">
+      <c r="B26" s="2" t="s">
         <v>113</v>
       </c>
       <c r="C26" t="s">
         <v>114</v>
       </c>
-      <c r="D26" s="2">
+      <c r="D26" s="3">
         <v>310</v>
       </c>
-      <c r="E26" s="2">
-        <v>34</v>
-      </c>
-      <c r="F26" s="1" t="s">
+      <c r="E26" s="3">
+        <v>34</v>
+      </c>
+      <c r="F26" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="G26" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="H26" s="1" t="s">
+      <c r="G26" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H26" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="I26" s="2">
+      <c r="I26" s="3">
         <v>10021</v>
       </c>
-      <c r="J26" s="1" t="s">
+      <c r="J26" s="2" t="s">
         <v>109</v>
       </c>
       <c r="K26" t="s">
@@ -2209,31 +2227,31 @@
       </c>
     </row>
     <row r="27" spans="2:11">
-      <c r="B27" s="1" t="s">
+      <c r="B27" s="2" t="s">
         <v>117</v>
       </c>
       <c r="C27" t="s">
         <v>118</v>
       </c>
-      <c r="D27" s="2">
+      <c r="D27" s="3">
         <v>310</v>
       </c>
-      <c r="E27" s="2">
-        <v>34</v>
-      </c>
-      <c r="F27" s="1" t="s">
+      <c r="E27" s="3">
+        <v>34</v>
+      </c>
+      <c r="F27" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="G27" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="H27" s="1" t="s">
+      <c r="G27" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H27" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="I27" s="2">
+      <c r="I27" s="3">
         <v>10022</v>
       </c>
-      <c r="J27" s="1" t="s">
+      <c r="J27" s="2" t="s">
         <v>113</v>
       </c>
       <c r="K27" t="s">
@@ -2241,28 +2259,28 @@
       </c>
     </row>
     <row r="28" spans="2:11">
-      <c r="B28" s="1" t="s">
+      <c r="B28" s="2" t="s">
         <v>121</v>
       </c>
       <c r="C28" t="s">
         <v>122</v>
       </c>
-      <c r="D28" s="2">
+      <c r="D28" s="3">
         <v>300</v>
       </c>
-      <c r="E28" s="2">
-        <v>34</v>
-      </c>
-      <c r="F28" s="1" t="s">
+      <c r="E28" s="3">
+        <v>34</v>
+      </c>
+      <c r="F28" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="G28" s="1" t="s">
+      <c r="G28" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="H28" s="1" t="s">
+      <c r="H28" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="J28" s="1" t="s">
+      <c r="J28" s="2" t="s">
         <v>117</v>
       </c>
       <c r="K28" t="s">

--- a/Config/HeroConfig.xlsx
+++ b/Config/HeroConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="15285" windowHeight="12825"/>
+    <workbookView windowWidth="15285" windowHeight="11655"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="125">
   <si>
     <t>##var</t>
   </si>
@@ -142,15 +142,12 @@
     <t>狠人</t>
   </si>
   <si>
-    <t>0.05</t>
+    <t>0.15</t>
   </si>
   <si>
     <t>People3</t>
   </si>
   <si>
-    <t>10002|100021</t>
-  </si>
-  <si>
     <t>造成的伤害+25%,且拥有15%暴击率</t>
   </si>
   <si>
@@ -206,9 +203,6 @@
   </si>
   <si>
     <t>武林高手</t>
-  </si>
-  <si>
-    <t>0.15</t>
   </si>
   <si>
     <t>People8</t>
@@ -1044,11 +1038,9 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1409,13 +1401,13 @@
   <cols>
     <col min="1" max="1" width="3.075" style="2" customWidth="1"/>
     <col min="2" max="2" width="4" style="2" customWidth="1"/>
-    <col min="3" max="3" width="9" customWidth="1"/>
+    <col min="3" max="3" width="9" style="3" customWidth="1"/>
     <col min="4" max="4" width="6.125" style="2" customWidth="1"/>
     <col min="5" max="5" width="6.25" style="2" customWidth="1"/>
     <col min="6" max="6" width="6.35" style="2" customWidth="1"/>
     <col min="7" max="7" width="7.88333333333333" style="2" customWidth="1"/>
     <col min="8" max="8" width="12" style="2" customWidth="1"/>
-    <col min="9" max="9" width="13.75" style="3" customWidth="1"/>
+    <col min="9" max="9" width="13.75" style="4" customWidth="1"/>
     <col min="10" max="10" width="4.41666666666667" style="2" customWidth="1"/>
     <col min="11" max="11" width="14.375" style="2" customWidth="1"/>
     <col min="12" max="12" width="34.75" style="2" customWidth="1"/>
@@ -1447,7 +1439,7 @@
       <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
@@ -1482,13 +1474,13 @@
       <c r="H2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="J2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="K2" s="4" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1517,7 +1509,7 @@
       <c r="H3" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="4" t="s">
         <v>22</v>
       </c>
       <c r="J3" s="2" t="s">
@@ -1534,10 +1526,10 @@
       <c r="C5" t="s">
         <v>26</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="4">
         <v>320</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5" s="4">
         <v>40</v>
       </c>
       <c r="F5" s="2" t="s">
@@ -1561,11 +1553,11 @@
       <c r="C6" t="s">
         <v>31</v>
       </c>
-      <c r="D6" s="3">
-        <v>300</v>
-      </c>
-      <c r="E6" s="3">
-        <v>34</v>
+      <c r="D6" s="4">
+        <v>260</v>
+      </c>
+      <c r="E6" s="4">
+        <v>38</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>27</v>
@@ -1576,7 +1568,7 @@
       <c r="H6" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="I6" s="3">
+      <c r="I6" s="4">
         <v>10001</v>
       </c>
       <c r="J6" s="2" t="s">
@@ -1593,11 +1585,11 @@
       <c r="C7" t="s">
         <v>35</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D7" s="4">
         <v>320</v>
       </c>
-      <c r="E7" s="3">
-        <v>34</v>
+      <c r="E7" s="4">
+        <v>27</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>36</v>
@@ -1608,28 +1600,28 @@
       <c r="H7" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="I7" s="3" t="s">
+      <c r="I7" s="4">
+        <v>10002</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="K7" s="2" t="s">
         <v>38</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="B8" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C8" t="s">
         <v>40</v>
       </c>
-      <c r="C8" t="s">
-        <v>41</v>
-      </c>
-      <c r="D8" s="3">
+      <c r="D8" s="4">
         <v>320</v>
       </c>
-      <c r="E8" s="3">
-        <v>34</v>
+      <c r="E8" s="4">
+        <v>32</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>27</v>
@@ -1638,30 +1630,30 @@
         <v>28</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="I8" s="3">
+        <v>41</v>
+      </c>
+      <c r="I8" s="4">
         <v>10003</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>34</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="B9" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C9" t="s">
         <v>44</v>
       </c>
-      <c r="C9" t="s">
-        <v>45</v>
-      </c>
-      <c r="D9" s="3">
+      <c r="D9" s="4">
         <v>320</v>
       </c>
-      <c r="E9" s="3">
-        <v>34</v>
+      <c r="E9" s="4">
+        <v>30</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>27</v>
@@ -1670,30 +1662,30 @@
         <v>28</v>
       </c>
       <c r="H9" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="I9" s="4">
+        <v>10004</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="K9" s="2" t="s">
         <v>46</v>
-      </c>
-      <c r="I9" s="3">
-        <v>10004</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="B10" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10" t="s">
         <v>48</v>
       </c>
-      <c r="C10" t="s">
-        <v>49</v>
-      </c>
-      <c r="D10" s="3">
+      <c r="D10" s="4">
         <v>320</v>
       </c>
-      <c r="E10" s="3">
-        <v>34</v>
+      <c r="E10" s="4">
+        <v>30</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>27</v>
@@ -1702,30 +1694,30 @@
         <v>28</v>
       </c>
       <c r="H10" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="I10" s="4">
+        <v>10005</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K10" s="2" t="s">
         <v>50</v>
-      </c>
-      <c r="I10" s="3">
-        <v>10005</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="B11" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C11" t="s">
         <v>52</v>
       </c>
-      <c r="C11" t="s">
-        <v>53</v>
-      </c>
-      <c r="D11" s="3">
+      <c r="D11" s="4">
         <v>330</v>
       </c>
-      <c r="E11" s="3">
-        <v>34</v>
+      <c r="E11" s="4">
+        <v>38</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>27</v>
@@ -1734,62 +1726,62 @@
         <v>28</v>
       </c>
       <c r="H11" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="I11" s="4">
+        <v>10006</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="K11" s="2" t="s">
         <v>54</v>
-      </c>
-      <c r="I11" s="3">
-        <v>10006</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="B12" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C12" t="s">
         <v>56</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" s="4">
+        <v>260</v>
+      </c>
+      <c r="E12" s="4">
+        <v>35</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H12" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="D12" s="3">
-        <v>320</v>
-      </c>
-      <c r="E12" s="3">
-        <v>34</v>
-      </c>
-      <c r="F12" s="2" t="s">
+      <c r="I12" s="4">
+        <v>10007</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="K12" t="s">
         <v>58</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="I12" s="3">
-        <v>10007</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="K12" s="4" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="B13" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C13" t="s">
-        <v>62</v>
-      </c>
-      <c r="D13" s="3">
-        <v>340</v>
-      </c>
-      <c r="E13" s="3">
-        <v>34</v>
+        <v>60</v>
+      </c>
+      <c r="D13" s="4">
+        <v>330</v>
+      </c>
+      <c r="E13" s="4">
+        <v>38</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>27</v>
@@ -1798,30 +1790,30 @@
         <v>28</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="I13" s="3">
+        <v>61</v>
+      </c>
+      <c r="I13" s="4">
         <v>10008</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K13" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="B14" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C14" t="s">
-        <v>66</v>
-      </c>
-      <c r="D14" s="3">
+        <v>64</v>
+      </c>
+      <c r="D14" s="4">
         <v>330</v>
       </c>
-      <c r="E14" s="3">
-        <v>34</v>
+      <c r="E14" s="4">
+        <v>38</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>27</v>
@@ -1830,30 +1822,30 @@
         <v>28</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="I14" s="3">
+        <v>65</v>
+      </c>
+      <c r="I14" s="4">
         <v>10009</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="15" spans="1:11">
       <c r="B15" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C15" t="s">
-        <v>70</v>
-      </c>
-      <c r="D15" s="3">
+        <v>68</v>
+      </c>
+      <c r="D15" s="4">
         <v>330</v>
       </c>
-      <c r="E15" s="3">
-        <v>34</v>
+      <c r="E15" s="4">
+        <v>38</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>27</v>
@@ -1862,30 +1854,30 @@
         <v>28</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="I15" s="3">
+        <v>69</v>
+      </c>
+      <c r="I15" s="4">
         <v>10010</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16" spans="1:11">
       <c r="B16" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C16" t="s">
-        <v>74</v>
-      </c>
-      <c r="D16" s="3">
-        <v>340</v>
-      </c>
-      <c r="E16" s="3">
-        <v>34</v>
+        <v>72</v>
+      </c>
+      <c r="D16" s="4">
+        <v>330</v>
+      </c>
+      <c r="E16" s="4">
+        <v>38</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>27</v>
@@ -1894,30 +1886,30 @@
         <v>28</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="I16" s="3">
+        <v>73</v>
+      </c>
+      <c r="I16" s="4">
         <v>10011</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="K16" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17" spans="2:11">
       <c r="B17" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C17" t="s">
-        <v>78</v>
-      </c>
-      <c r="D17" s="3">
+        <v>76</v>
+      </c>
+      <c r="D17" s="4">
         <v>300</v>
       </c>
-      <c r="E17" s="3">
-        <v>34</v>
+      <c r="E17" s="4">
+        <v>33</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>27</v>
@@ -1926,30 +1918,30 @@
         <v>28</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="I17" s="3">
+        <v>77</v>
+      </c>
+      <c r="I17" s="4">
         <v>10012</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="K17" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18" spans="2:11">
       <c r="B18" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C18" t="s">
-        <v>82</v>
-      </c>
-      <c r="D18" s="3">
+        <v>80</v>
+      </c>
+      <c r="D18" s="4">
         <v>320</v>
       </c>
-      <c r="E18" s="3">
-        <v>34</v>
+      <c r="E18" s="4">
+        <v>38</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>27</v>
@@ -1958,30 +1950,30 @@
         <v>28</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="I18" s="3">
+        <v>81</v>
+      </c>
+      <c r="I18" s="4">
         <v>10013</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="K18" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="19" spans="2:11">
       <c r="B19" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C19" t="s">
-        <v>86</v>
-      </c>
-      <c r="D19" s="3">
+        <v>84</v>
+      </c>
+      <c r="D19" s="4">
         <v>320</v>
       </c>
-      <c r="E19" s="3">
-        <v>34</v>
+      <c r="E19" s="4">
+        <v>36</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>27</v>
@@ -1990,30 +1982,30 @@
         <v>28</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="I19" s="3">
+        <v>85</v>
+      </c>
+      <c r="I19" s="4">
         <v>10014</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="K19" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="20" spans="2:11">
       <c r="B20" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C20" t="s">
-        <v>90</v>
-      </c>
-      <c r="D20" s="3">
+        <v>88</v>
+      </c>
+      <c r="D20" s="4">
         <v>300</v>
       </c>
-      <c r="E20" s="3">
-        <v>34</v>
+      <c r="E20" s="4">
+        <v>38</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>27</v>
@@ -2022,30 +2014,30 @@
         <v>28</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="I20" s="3">
+        <v>89</v>
+      </c>
+      <c r="I20" s="4">
         <v>10015</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="K20" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="21" spans="2:11">
       <c r="B21" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C21" t="s">
-        <v>94</v>
-      </c>
-      <c r="D21" s="3">
+        <v>92</v>
+      </c>
+      <c r="D21" s="4">
         <v>330</v>
       </c>
-      <c r="E21" s="3">
-        <v>34</v>
+      <c r="E21" s="4">
+        <v>38</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>27</v>
@@ -2054,30 +2046,30 @@
         <v>28</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="I21" s="3">
+        <v>93</v>
+      </c>
+      <c r="I21" s="4">
         <v>10016</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="K21" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" spans="2:11">
       <c r="B22" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D22" s="6">
         <v>320</v>
       </c>
       <c r="E22" s="6">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>27</v>
@@ -2086,30 +2078,30 @@
         <v>28</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="I22" s="6">
         <v>10017</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="K22" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="23" spans="2:11">
       <c r="B23" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C23" t="s">
-        <v>102</v>
-      </c>
-      <c r="D23" s="3">
+        <v>100</v>
+      </c>
+      <c r="D23" s="4">
         <v>330</v>
       </c>
-      <c r="E23" s="3">
-        <v>34</v>
+      <c r="E23" s="4">
+        <v>38</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>27</v>
@@ -2118,30 +2110,30 @@
         <v>28</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="I23" s="3">
+        <v>101</v>
+      </c>
+      <c r="I23" s="4">
         <v>10018</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="K23" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="24" spans="2:11">
       <c r="B24" s="2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C24" t="s">
-        <v>106</v>
-      </c>
-      <c r="D24" s="3">
+        <v>104</v>
+      </c>
+      <c r="D24" s="4">
         <v>300</v>
       </c>
-      <c r="E24" s="3">
-        <v>34</v>
+      <c r="E24" s="4">
+        <v>30</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>27</v>
@@ -2150,30 +2142,30 @@
         <v>28</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="I24" s="3">
+        <v>105</v>
+      </c>
+      <c r="I24" s="4">
         <v>10019</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="K24" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="25" spans="2:11">
       <c r="B25" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C25" t="s">
-        <v>110</v>
-      </c>
-      <c r="D25" s="3">
+        <v>108</v>
+      </c>
+      <c r="D25" s="4">
         <v>310</v>
       </c>
-      <c r="E25" s="3">
-        <v>34</v>
+      <c r="E25" s="4">
+        <v>33</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>27</v>
@@ -2182,29 +2174,29 @@
         <v>28</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="I25" s="3">
+        <v>109</v>
+      </c>
+      <c r="I25" s="4">
         <v>10020</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="K25" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="26" spans="2:11">
       <c r="B26" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C26" t="s">
-        <v>114</v>
-      </c>
-      <c r="D26" s="3">
+        <v>112</v>
+      </c>
+      <c r="D26" s="4">
         <v>310</v>
       </c>
-      <c r="E26" s="3">
+      <c r="E26" s="4">
         <v>34</v>
       </c>
       <c r="F26" s="2" t="s">
@@ -2214,30 +2206,30 @@
         <v>28</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="I26" s="3">
+        <v>113</v>
+      </c>
+      <c r="I26" s="4">
         <v>10021</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="K26" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="27" spans="2:11">
       <c r="B27" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C27" t="s">
-        <v>118</v>
-      </c>
-      <c r="D27" s="3">
+        <v>116</v>
+      </c>
+      <c r="D27" s="4">
         <v>310</v>
       </c>
-      <c r="E27" s="3">
-        <v>34</v>
+      <c r="E27" s="4">
+        <v>32</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>27</v>
@@ -2246,45 +2238,45 @@
         <v>28</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="I27" s="3">
+        <v>117</v>
+      </c>
+      <c r="I27" s="4">
         <v>10022</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="K27" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="28" spans="2:11">
       <c r="B28" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C28" t="s">
+        <v>120</v>
+      </c>
+      <c r="D28" s="4">
+        <v>300</v>
+      </c>
+      <c r="E28" s="4">
+        <v>26</v>
+      </c>
+      <c r="F28" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="C28" t="s">
+      <c r="G28" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="D28" s="3">
-        <v>300</v>
-      </c>
-      <c r="E28" s="3">
-        <v>34</v>
-      </c>
-      <c r="F28" s="2" t="s">
+      <c r="H28" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="G28" s="2" t="s">
+      <c r="J28" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="K28" t="s">
         <v>124</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="J28" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="K28" t="s">
-        <v>126</v>
       </c>
     </row>
   </sheetData>

--- a/Config/HeroConfig.xlsx
+++ b/Config/HeroConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="15285" windowHeight="11655"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="78">
   <si>
     <t>##var</t>
   </si>
@@ -127,286 +127,145 @@
     <t>平平无奇之人</t>
   </si>
   <si>
-    <t>大壮</t>
+    <t>猎人</t>
+  </si>
+  <si>
+    <t>0.1</t>
   </si>
   <si>
     <t>People2</t>
   </si>
   <si>
-    <t>受到的伤害-25%</t>
+    <t>201|202</t>
+  </si>
+  <si>
+    <t>拥有10%暴击率,且攻击时有35%概率追加1次攻击;但受到的伤害+15%</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>狠人</t>
+    <t>暗灵法师</t>
+  </si>
+  <si>
+    <t>People3</t>
+  </si>
+  <si>
+    <t>301|302|303</t>
+  </si>
+  <si>
+    <t>攻击会对其他人造成10%的分裂伤害,每击杀1名敌人该效果就提高3%(精英/领主提高6%);但无法暴击</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>狂战士</t>
+  </si>
+  <si>
+    <t>People4</t>
+  </si>
+  <si>
+    <t>401|402|403</t>
+  </si>
+  <si>
+    <t>每降低80血量都会使伤害提高5%,最多叠加20层,且攻击时附带8%的吸血;但无法通过圣物回复血量</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>盗贼</t>
+  </si>
+  <si>
+    <t>0.2</t>
+  </si>
+  <si>
+    <t>People5</t>
+  </si>
+  <si>
+    <t>501|502|503</t>
+  </si>
+  <si>
+    <t>拥有20%暴击率,每击杀1名敌人永久获得3点攻击力,攻击力＞150后,攻击变化为群体伤害;但对领主/精英敌人伤害-25%</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>灰烬术士</t>
   </si>
   <si>
     <t>0.15</t>
   </si>
   <si>
-    <t>People3</t>
-  </si>
-  <si>
-    <t>造成的伤害+25%,且拥有15%暴击率</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>多面手</t>
-  </si>
-  <si>
-    <t>People4</t>
-  </si>
-  <si>
-    <t>攻击时,对其他人造成30%的伤害</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>射手</t>
-  </si>
-  <si>
-    <t>People5</t>
-  </si>
-  <si>
-    <t>攻击时,有35%概率额外攻击1次</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>灰烬术士</t>
+    <t>1.5</t>
   </si>
   <si>
     <t>People6</t>
   </si>
   <si>
-    <t>攻击时,对所有人造成40%的群体伤害</t>
+    <t>拥有15%暴击率,攻击时对所有人造成50%的群体伤害;但暴击伤害-50%</t>
   </si>
   <si>
     <t>7</t>
   </si>
   <si>
-    <t>富豪</t>
+    <t>萨满祭司</t>
   </si>
   <si>
     <t>People7</t>
   </si>
   <si>
-    <t>初始额外拥有150金币</t>
+    <t>701|702|703</t>
+  </si>
+  <si>
+    <t>通过圣物获得的生命回复效果+50%,对精英/领主伤害+50%;但每回合开始时会受到场上当前敌人数量x2的伤害</t>
   </si>
   <si>
     <t>8</t>
   </si>
   <si>
-    <t>武林高手</t>
+    <t>圣骑士</t>
   </si>
   <si>
     <t>People8</t>
   </si>
   <si>
-    <t>初始拥有15%暴击率,25%闪避率</t>
+    <t>801|802|803</t>
+  </si>
+  <si>
+    <t>受到的伤害-25%,每回合开始会发动1次[圣光燃烧],亮牌时是对子牌型且获得胜利,也会发动[圣光燃烧];但无法闪避(圣光燃烧:对场上所有敌人造成1次圣骑士当前攻击力50%的伤害,每发动1次会使后续攻击力给予伤害+10%)</t>
   </si>
   <si>
     <t>9</t>
   </si>
   <si>
-    <t>赌神</t>
+    <t>旅者</t>
   </si>
   <si>
     <t>People9</t>
   </si>
   <si>
-    <t>每关[搓牌]使用次数+1</t>
+    <t>901|902|903</t>
+  </si>
+  <si>
+    <t>商店中的所有圣物的购买价格-20%,每击杀1名敌人会获得50金币;但无法通过圣物获得金币</t>
   </si>
   <si>
     <t>10</t>
   </si>
   <si>
-    <t>暴发户</t>
+    <t>武僧</t>
   </si>
   <si>
     <t>People10</t>
   </si>
   <si>
-    <t>商店刷到史诗及以上品质的圣物概率+10%</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>关系户</t>
-  </si>
-  <si>
-    <t>People11</t>
-  </si>
-  <si>
-    <t>商店中的所有圣物的购买价格-20%</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>经济教授</t>
-  </si>
-  <si>
-    <t>People12</t>
-  </si>
-  <si>
-    <t>每关结算时获得的金币数量+30%</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>死灵法师</t>
-  </si>
-  <si>
-    <t>People13</t>
-  </si>
-  <si>
-    <t>对精英、领主造成的伤害+50%</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>裁决使</t>
-  </si>
-  <si>
-    <t>People14</t>
-  </si>
-  <si>
-    <t>攻击血量小于10%的非领主敌人时,有20%概率直接斩杀</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>亡命徒</t>
-  </si>
-  <si>
-    <t>People15</t>
-  </si>
-  <si>
-    <t>自身血量小于20%时,造成的伤害+50%</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>囤货王</t>
-  </si>
-  <si>
-    <t>People16</t>
-  </si>
-  <si>
-    <t>圣物携带上限+1</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>阴阳师</t>
-  </si>
-  <si>
-    <t>People17</t>
-  </si>
-  <si>
-    <t>每关[透视]使用次数+1</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>营养师</t>
-  </si>
-  <si>
-    <t>People18</t>
-  </si>
-  <si>
-    <t>每回合开始时回复自身2%血量</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>拾荒者</t>
-  </si>
-  <si>
-    <t>People19</t>
-  </si>
-  <si>
-    <t>每击杀1名敌人,额外获得20金币</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>修炼者</t>
-  </si>
-  <si>
-    <t>People20</t>
-  </si>
-  <si>
-    <t>每击杀1名敌人,额外提高2点攻击力</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>决斗大师</t>
-  </si>
-  <si>
-    <t>People21</t>
-  </si>
-  <si>
-    <t>场上只剩1名敌人时,造成的伤害+50%</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>孩子王</t>
-  </si>
-  <si>
-    <t>People22</t>
-  </si>
-  <si>
-    <t>场上敌人多于1名时,造成的伤害+30%</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>急性子</t>
-  </si>
-  <si>
-    <t>People23</t>
-  </si>
-  <si>
-    <t>每关首回合比牌时,结算时的倍率+5</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>锦鲤</t>
-  </si>
-  <si>
-    <t>0.4</t>
-  </si>
-  <si>
-    <t>2.4</t>
-  </si>
-  <si>
-    <t>People24</t>
-  </si>
-  <si>
-    <t>暴击率+40%,暴击伤害+40%</t>
+    <t>1001|1002|1003</t>
+  </si>
+  <si>
+    <t>拥有25%闪避率,且闪避后会对该敌人进行1次反击,反击伤害为自身攻击力的200%;但每关[搓牌]使用次数-1</t>
   </si>
 </sst>
 </file>
@@ -572,18 +431,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -904,7 +757,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
@@ -928,16 +781,16 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="6">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
@@ -946,94 +799,91 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="26" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="30" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1042,11 +892,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1396,888 +1243,449 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K28"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="3.075" style="2" customWidth="1"/>
-    <col min="2" max="2" width="4" style="2" customWidth="1"/>
-    <col min="3" max="3" width="9" style="3" customWidth="1"/>
-    <col min="4" max="4" width="6.125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="6.25" style="2" customWidth="1"/>
-    <col min="6" max="6" width="6.35" style="2" customWidth="1"/>
-    <col min="7" max="7" width="7.88333333333333" style="2" customWidth="1"/>
-    <col min="8" max="8" width="12" style="2" customWidth="1"/>
-    <col min="9" max="9" width="13.75" style="4" customWidth="1"/>
-    <col min="10" max="10" width="4.41666666666667" style="2" customWidth="1"/>
-    <col min="11" max="11" width="14.375" style="2" customWidth="1"/>
-    <col min="12" max="12" width="34.75" style="2" customWidth="1"/>
-    <col min="13" max="16384" width="9" style="2" customWidth="1"/>
+    <col min="1" max="1" width="3.075" style="1" customWidth="1"/>
+    <col min="2" max="2" width="4" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9" style="2" customWidth="1"/>
+    <col min="4" max="4" width="6.125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="6.25" style="1" customWidth="1"/>
+    <col min="6" max="6" width="6.35" style="1" customWidth="1"/>
+    <col min="7" max="7" width="7.88333333333333" style="1" customWidth="1"/>
+    <col min="8" max="8" width="12" style="1" customWidth="1"/>
+    <col min="9" max="9" width="13.75" style="3" customWidth="1"/>
+    <col min="10" max="10" width="4.41666666666667" style="1" customWidth="1"/>
+    <col min="11" max="11" width="14.375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="34.75" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="9" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:11">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C2" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="I2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="J2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="K2" s="3" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:11">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C3" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="I3" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="J3" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="K3" s="1" t="s">
         <v>24</v>
       </c>
     </row>
+    <row r="4" ht="14.25"/>
     <row r="5" spans="1:11">
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D5" s="3">
         <v>320</v>
       </c>
-      <c r="E5" s="4">
+      <c r="E5" s="3">
         <v>40</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="G5" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="H5" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="I5" s="2"/>
-      <c r="K5" s="2" t="s">
+      <c r="I5" s="1"/>
+      <c r="K5" s="1" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:11">
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D6" s="3">
         <v>260</v>
       </c>
-      <c r="E6" s="4">
+      <c r="E6" s="3">
         <v>38</v>
       </c>
-      <c r="F6" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="G6" s="2" t="s">
+      <c r="F6" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G6" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="H6" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I6" s="4">
-        <v>10001</v>
-      </c>
-      <c r="J6" s="2" t="s">
+      <c r="H6" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="J6" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K6" s="2" t="s">
-        <v>33</v>
+      <c r="K6" s="4" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:11">
-      <c r="B7" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C7" t="s">
-        <v>35</v>
-      </c>
-      <c r="D7" s="4">
+      <c r="B7" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D7" s="3">
         <v>320</v>
       </c>
-      <c r="E7" s="4">
+      <c r="E7" s="3">
         <v>27</v>
       </c>
-      <c r="F7" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="G7" s="2" t="s">
+      <c r="F7" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G7" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="H7" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="I7" s="4">
-        <v>10002</v>
-      </c>
-      <c r="J7" s="2" t="s">
+      <c r="H7" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="J7" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="K7" s="2" t="s">
-        <v>38</v>
+      <c r="K7" s="4" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="8" spans="1:11">
-      <c r="B8" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C8" t="s">
-        <v>40</v>
-      </c>
-      <c r="D8" s="4">
+      <c r="B8" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D8" s="3">
         <v>320</v>
       </c>
-      <c r="E8" s="4">
+      <c r="E8" s="3">
         <v>32</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="F8" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G8" s="2" t="s">
+      <c r="G8" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="H8" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="I8" s="4">
-        <v>10003</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>42</v>
+      <c r="H8" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="K8" s="4" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:11">
-      <c r="B9" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C9" t="s">
-        <v>44</v>
-      </c>
-      <c r="D9" s="4">
+      <c r="B9" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D9" s="3">
         <v>320</v>
       </c>
-      <c r="E9" s="4">
+      <c r="E9" s="3">
         <v>30</v>
       </c>
-      <c r="F9" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="G9" s="2" t="s">
+      <c r="F9" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G9" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="H9" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="I9" s="4">
-        <v>10004</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>46</v>
+      <c r="H9" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="K9" s="4" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="10" spans="1:11">
-      <c r="B10" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C10" t="s">
-        <v>48</v>
-      </c>
-      <c r="D10" s="4">
+      <c r="B10" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D10" s="3">
         <v>320</v>
       </c>
-      <c r="E10" s="4">
+      <c r="E10" s="3">
         <v>30</v>
       </c>
-      <c r="F10" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="I10" s="4">
-        <v>10005</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>50</v>
+      <c r="F10" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="I10" s="3">
+        <v>601</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="K10" s="4" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="11" spans="1:11">
-      <c r="B11" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C11" t="s">
+      <c r="B11" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D11" s="3">
+        <v>330</v>
+      </c>
+      <c r="E11" s="3">
+        <v>38</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="J11" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D11" s="4">
-        <v>330</v>
-      </c>
-      <c r="E11" s="4">
-        <v>38</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="I11" s="4">
-        <v>10006</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>54</v>
+      <c r="K11" s="4" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="12" spans="1:11">
-      <c r="B12" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C12" t="s">
-        <v>56</v>
-      </c>
-      <c r="D12" s="4">
+      <c r="B12" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D12" s="3">
         <v>260</v>
       </c>
-      <c r="E12" s="4">
+      <c r="E12" s="3">
         <v>35</v>
       </c>
-      <c r="F12" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="G12" s="2" t="s">
+      <c r="F12" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G12" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="H12" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="I12" s="4">
-        <v>10007</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="K12" t="s">
+      <c r="H12" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="J12" s="1" t="s">
         <v>58</v>
+      </c>
+      <c r="K12" s="4" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="13" spans="1:11">
-      <c r="B13" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C13" t="s">
-        <v>60</v>
-      </c>
-      <c r="D13" s="4">
+      <c r="B13" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="D13" s="3">
         <v>330</v>
       </c>
-      <c r="E13" s="4">
+      <c r="E13" s="3">
         <v>38</v>
       </c>
-      <c r="F13" s="2" t="s">
+      <c r="F13" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G13" s="2" t="s">
+      <c r="G13" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="H13" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="I13" s="4">
-        <v>10008</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>55</v>
+      <c r="H13" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>63</v>
       </c>
       <c r="K13" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
     </row>
     <row r="14" spans="1:11">
-      <c r="B14" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C14" t="s">
-        <v>64</v>
-      </c>
-      <c r="D14" s="4">
+      <c r="B14" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="D14" s="3">
         <v>330</v>
       </c>
-      <c r="E14" s="4">
+      <c r="E14" s="3">
         <v>38</v>
       </c>
-      <c r="F14" s="2" t="s">
+      <c r="F14" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G14" s="2" t="s">
+      <c r="G14" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="H14" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="I14" s="4">
-        <v>10009</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="K14" s="2" t="s">
-        <v>66</v>
+      <c r="H14" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="15" spans="1:11">
-      <c r="B15" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="C15" t="s">
-        <v>68</v>
-      </c>
-      <c r="D15" s="4">
-        <v>330</v>
-      </c>
-      <c r="E15" s="4">
-        <v>38</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="I15" s="4">
-        <v>10010</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="K15" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11">
-      <c r="B16" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C16" t="s">
-        <v>72</v>
-      </c>
-      <c r="D16" s="4">
-        <v>330</v>
-      </c>
-      <c r="E16" s="4">
-        <v>38</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="I16" s="4">
-        <v>10011</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="K16" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="17" spans="2:11">
-      <c r="B17" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C17" t="s">
-        <v>76</v>
-      </c>
-      <c r="D17" s="4">
-        <v>300</v>
-      </c>
-      <c r="E17" s="4">
-        <v>33</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="I17" s="4">
-        <v>10012</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="K17" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="18" spans="2:11">
-      <c r="B18" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="C18" t="s">
-        <v>80</v>
-      </c>
-      <c r="D18" s="4">
-        <v>320</v>
-      </c>
-      <c r="E18" s="4">
-        <v>38</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="I18" s="4">
-        <v>10013</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="K18" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="19" spans="2:11">
-      <c r="B19" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="C19" t="s">
-        <v>84</v>
-      </c>
-      <c r="D19" s="4">
-        <v>320</v>
-      </c>
-      <c r="E19" s="4">
-        <v>36</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="I19" s="4">
-        <v>10014</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="K19" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="20" spans="2:11">
-      <c r="B20" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C20" t="s">
-        <v>88</v>
-      </c>
-      <c r="D20" s="4">
-        <v>300</v>
-      </c>
-      <c r="E20" s="4">
-        <v>38</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="I20" s="4">
-        <v>10015</v>
-      </c>
-      <c r="J20" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="K20" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="21" spans="2:11">
-      <c r="B21" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="C21" t="s">
-        <v>92</v>
-      </c>
-      <c r="D21" s="4">
-        <v>330</v>
-      </c>
-      <c r="E21" s="4">
-        <v>38</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="I21" s="4">
-        <v>10016</v>
-      </c>
-      <c r="J21" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="K21" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="22" s="1" customFormat="1" spans="2:11">
-      <c r="B22" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="D22" s="6">
-        <v>320</v>
-      </c>
-      <c r="E22" s="6">
-        <v>38</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="G22" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="H22" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="I22" s="6">
-        <v>10017</v>
-      </c>
-      <c r="J22" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="K22" s="5" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="23" spans="2:11">
-      <c r="B23" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="C23" t="s">
-        <v>100</v>
-      </c>
-      <c r="D23" s="4">
-        <v>330</v>
-      </c>
-      <c r="E23" s="4">
-        <v>38</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="I23" s="4">
-        <v>10018</v>
-      </c>
-      <c r="J23" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="K23" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="24" spans="2:11">
-      <c r="B24" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="C24" t="s">
-        <v>104</v>
-      </c>
-      <c r="D24" s="4">
-        <v>300</v>
-      </c>
-      <c r="E24" s="4">
-        <v>30</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="I24" s="4">
-        <v>10019</v>
-      </c>
-      <c r="J24" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="K24" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="25" spans="2:11">
-      <c r="B25" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="C25" t="s">
-        <v>108</v>
-      </c>
-      <c r="D25" s="4">
-        <v>310</v>
-      </c>
-      <c r="E25" s="4">
-        <v>33</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="I25" s="4">
-        <v>10020</v>
-      </c>
-      <c r="J25" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="K25" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="26" spans="2:11">
-      <c r="B26" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="C26" t="s">
-        <v>112</v>
-      </c>
-      <c r="D26" s="4">
-        <v>310</v>
-      </c>
-      <c r="E26" s="4">
-        <v>34</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="I26" s="4">
-        <v>10021</v>
-      </c>
-      <c r="J26" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="K26" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="27" spans="2:11">
-      <c r="B27" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="C27" t="s">
-        <v>116</v>
-      </c>
-      <c r="D27" s="4">
-        <v>310</v>
-      </c>
-      <c r="E27" s="4">
-        <v>32</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="I27" s="4">
-        <v>10022</v>
-      </c>
-      <c r="J27" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="K27" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="28" spans="2:11">
-      <c r="B28" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="C28" t="s">
-        <v>120</v>
-      </c>
-      <c r="D28" s="4">
-        <v>300</v>
-      </c>
-      <c r="E28" s="4">
-        <v>26</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="J28" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="K28" t="s">
-        <v>124</v>
-      </c>
+      <c r="C15"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Config/HeroConfig.xlsx
+++ b/Config/HeroConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="10920" windowHeight="11340"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -881,7 +881,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -891,9 +891,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1366,12 +1363,12 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" ht="14.25"/>
+    <row r="4" ht="14.25" customHeight="1"/>
     <row r="5" spans="1:11">
       <c r="B5" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" t="s">
         <v>26</v>
       </c>
       <c r="D5" s="3">
@@ -1398,14 +1395,14 @@
       <c r="B6" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" t="s">
         <v>31</v>
       </c>
       <c r="D6" s="3">
-        <v>260</v>
+        <v>370</v>
       </c>
       <c r="E6" s="3">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>32</v>
@@ -1422,7 +1419,7 @@
       <c r="J6" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K6" s="4" t="s">
+      <c r="K6" t="s">
         <v>35</v>
       </c>
     </row>
@@ -1430,14 +1427,14 @@
       <c r="B7" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" t="s">
         <v>37</v>
       </c>
       <c r="D7" s="3">
         <v>320</v>
       </c>
       <c r="E7" s="3">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>27</v>
@@ -1454,7 +1451,7 @@
       <c r="J7" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="K7" s="4" t="s">
+      <c r="K7" t="s">
         <v>40</v>
       </c>
     </row>
@@ -1462,14 +1459,14 @@
       <c r="B8" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" t="s">
         <v>42</v>
       </c>
       <c r="D8" s="3">
         <v>320</v>
       </c>
       <c r="E8" s="3">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>27</v>
@@ -1486,7 +1483,7 @@
       <c r="J8" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="K8" s="4" t="s">
+      <c r="K8" t="s">
         <v>45</v>
       </c>
     </row>
@@ -1494,14 +1491,14 @@
       <c r="B9" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" t="s">
         <v>47</v>
       </c>
       <c r="D9" s="3">
         <v>320</v>
       </c>
       <c r="E9" s="3">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>48</v>
@@ -1518,7 +1515,7 @@
       <c r="J9" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="K9" s="4" t="s">
+      <c r="K9" t="s">
         <v>51</v>
       </c>
     </row>
@@ -1526,14 +1523,14 @@
       <c r="B10" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" t="s">
         <v>53</v>
       </c>
       <c r="D10" s="3">
         <v>320</v>
       </c>
       <c r="E10" s="3">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>54</v>
@@ -1550,7 +1547,7 @@
       <c r="J10" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="K10" s="4" t="s">
+      <c r="K10" t="s">
         <v>57</v>
       </c>
     </row>
@@ -1558,14 +1555,14 @@
       <c r="B11" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" t="s">
         <v>59</v>
       </c>
       <c r="D11" s="3">
         <v>330</v>
       </c>
       <c r="E11" s="3">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>27</v>
@@ -1582,7 +1579,7 @@
       <c r="J11" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="K11" s="4" t="s">
+      <c r="K11" t="s">
         <v>62</v>
       </c>
     </row>
@@ -1590,14 +1587,14 @@
       <c r="B12" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" t="s">
         <v>64</v>
       </c>
       <c r="D12" s="3">
         <v>260</v>
       </c>
       <c r="E12" s="3">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>27</v>
@@ -1614,7 +1611,7 @@
       <c r="J12" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="K12" s="4" t="s">
+      <c r="K12" t="s">
         <v>67</v>
       </c>
     </row>
@@ -1622,7 +1619,7 @@
       <c r="B13" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" t="s">
         <v>69</v>
       </c>
       <c r="D13" s="3">
@@ -1654,14 +1651,14 @@
       <c r="B14" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" t="s">
         <v>74</v>
       </c>
       <c r="D14" s="3">
         <v>330</v>
       </c>
       <c r="E14" s="3">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>27</v>

--- a/Config/HeroConfig.xlsx
+++ b/Config/HeroConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="10920" windowHeight="11340"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="81">
   <si>
     <t>##var</t>
   </si>
@@ -61,6 +61,9 @@
     <t>HeroEntryId</t>
   </si>
   <si>
+    <t>HeroEffects</t>
+  </si>
+  <si>
     <t>UnlockCondition</t>
   </si>
   <si>
@@ -103,6 +106,9 @@
     <t>英雄机制id</t>
   </si>
   <si>
+    <t>英雄特效Id</t>
+  </si>
+  <si>
     <t>解锁难度条件</t>
   </si>
   <si>
@@ -122,6 +128,9 @@
   </si>
   <si>
     <t>People1</t>
+  </si>
+  <si>
+    <t>101|201</t>
   </si>
   <si>
     <t>平平无奇之人</t>
@@ -1240,7 +1249,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="3.075" style="1" customWidth="1"/>
@@ -1252,13 +1261,14 @@
     <col min="7" max="7" width="7.88333333333333" style="1" customWidth="1"/>
     <col min="8" max="8" width="12" style="1" customWidth="1"/>
     <col min="9" max="9" width="13.75" style="3" customWidth="1"/>
-    <col min="10" max="10" width="4.41666666666667" style="1" customWidth="1"/>
-    <col min="11" max="11" width="14.375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="34.75" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="9" style="1" customWidth="1"/>
+    <col min="10" max="10" width="11" style="1" customWidth="1"/>
+    <col min="11" max="11" width="4.41666666666667" style="1" customWidth="1"/>
+    <col min="12" max="12" width="14.375" style="1" customWidth="1"/>
+    <col min="13" max="13" width="34.75" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="9" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1292,84 +1302,93 @@
       <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="E2" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="I2" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="K2" s="3" t="s">
         <v>13</v>
       </c>
+      <c r="L2" s="3" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:12">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1"/>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:12">
       <c r="B5" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D5" s="3">
         <v>320</v>
@@ -1378,25 +1397,28 @@
         <v>40</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I5" s="1"/>
-      <c r="K5" s="1" t="s">
+      <c r="J5" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="B6" s="1" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="6" spans="1:11">
-      <c r="B6" s="1" t="s">
-        <v>28</v>
-      </c>
       <c r="C6" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D6" s="3">
         <v>370</v>
@@ -1405,30 +1427,33 @@
         <v>27</v>
       </c>
       <c r="F6" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="J6" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="G6" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K6" t="s">
-        <v>35</v>
+      <c r="K6" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L6" t="s">
+        <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:12">
       <c r="B7" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C7" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D7" s="3">
         <v>320</v>
@@ -1437,30 +1462,33 @@
         <v>30</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="K7" t="s">
-        <v>40</v>
+        <v>32</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="L7" t="s">
+        <v>43</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:12">
       <c r="B8" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C8" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D8" s="3">
         <v>320</v>
@@ -1469,30 +1497,33 @@
         <v>31</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="K8" t="s">
-        <v>45</v>
+        <v>32</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="L8" t="s">
+        <v>48</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:12">
       <c r="B9" s="1" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C9" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D9" s="3">
         <v>320</v>
@@ -1501,30 +1532,33 @@
         <v>28</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="K9" t="s">
-        <v>51</v>
+        <v>32</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="L9" t="s">
+        <v>54</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:12">
       <c r="B10" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C10" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D10" s="3">
         <v>320</v>
@@ -1533,30 +1567,33 @@
         <v>27</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="I10" s="3">
         <v>601</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="K10" t="s">
-        <v>57</v>
+        <v>32</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="L10" t="s">
+        <v>60</v>
       </c>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:12">
       <c r="B11" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C11" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D11" s="3">
         <v>330</v>
@@ -1565,30 +1602,33 @@
         <v>33</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="K11" t="s">
-        <v>62</v>
+        <v>32</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="L11" t="s">
+        <v>65</v>
       </c>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:12">
       <c r="B12" s="1" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C12" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D12" s="3">
         <v>260</v>
@@ -1597,30 +1637,33 @@
         <v>30</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="K12" t="s">
-        <v>67</v>
+        <v>32</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="L12" t="s">
+        <v>70</v>
       </c>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:12">
       <c r="B13" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C13" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D13" s="3">
         <v>330</v>
@@ -1629,30 +1672,33 @@
         <v>38</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="K13" t="s">
-        <v>72</v>
+        <v>32</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="L13" t="s">
+        <v>75</v>
       </c>
     </row>
-    <row r="14" spans="1:11">
+    <row r="14" spans="1:12">
       <c r="B14" s="1" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C14" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D14" s="3">
         <v>330</v>
@@ -1661,25 +1707,28 @@
         <v>33</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>68</v>
+        <v>32</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>77</v>
+        <v>71</v>
+      </c>
+      <c r="L14" s="1" t="s">
+        <v>80</v>
       </c>
     </row>
-    <row r="15" spans="1:11">
+    <row r="15" spans="1:12">
       <c r="C15"/>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>

--- a/Config/HeroConfig.xlsx
+++ b/Config/HeroConfig.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="82">
   <si>
     <t>##var</t>
   </si>
@@ -130,24 +130,24 @@
     <t>People1</t>
   </si>
   <si>
+    <t>平平无奇之人</t>
+  </si>
+  <si>
+    <t>猎人</t>
+  </si>
+  <si>
+    <t>0.1</t>
+  </si>
+  <si>
+    <t>People2</t>
+  </si>
+  <si>
+    <t>201|202</t>
+  </si>
+  <si>
     <t>101|201</t>
   </si>
   <si>
-    <t>平平无奇之人</t>
-  </si>
-  <si>
-    <t>猎人</t>
-  </si>
-  <si>
-    <t>0.1</t>
-  </si>
-  <si>
-    <t>People2</t>
-  </si>
-  <si>
-    <t>201|202</t>
-  </si>
-  <si>
     <t>拥有10%暴击率,且攻击时有35%概率追加1次攻击;但受到的伤害+15%</t>
   </si>
   <si>
@@ -163,6 +163,9 @@
     <t>301|302|303</t>
   </si>
   <si>
+    <t>102|103|104|202</t>
+  </si>
+  <si>
     <t>攻击会对其他人造成10%的分裂伤害,每击杀1名敌人该效果就提高3%(精英/领主提高6%);但无法暴击</t>
   </si>
   <si>
@@ -244,7 +247,7 @@
     <t>801|802|803</t>
   </si>
   <si>
-    <t>受到的伤害-25%,每回合开始会发动1次[圣光燃烧],亮牌时是对子牌型且获得胜利,也会发动[圣光燃烧];但无法闪避(圣光燃烧:对场上所有敌人造成1次圣骑士当前攻击力50%的伤害,每发动1次会使后续攻击力给予伤害+10%)</t>
+    <t>受到伤害-25%,每回合开始会发动1次[圣光燃烧],比牌时若是对子且获得胜利,也会发动[圣光燃烧];但无法闪避(圣光燃烧:对场上所有敌人造成1次当前攻击力50%的伤害,每发动1次会使后续给予伤害+10%)</t>
   </si>
   <si>
     <t>9</t>
@@ -1406,11 +1409,8 @@
         <v>31</v>
       </c>
       <c r="I5" s="1"/>
-      <c r="J5" s="1" t="s">
+      <c r="L5" s="1" t="s">
         <v>32</v>
-      </c>
-      <c r="L5" s="1" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -1418,7 +1418,7 @@
         <v>30</v>
       </c>
       <c r="C6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D6" s="3">
         <v>370</v>
@@ -1427,19 +1427,19 @@
         <v>27</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>30</v>
       </c>
       <c r="H6" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I6" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="I6" s="3" t="s">
+      <c r="J6" s="1" t="s">
         <v>37</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>32</v>
       </c>
       <c r="K6" s="1" t="s">
         <v>27</v>
@@ -1474,21 +1474,21 @@
         <v>42</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="K7" s="1" t="s">
         <v>30</v>
       </c>
       <c r="L7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8" spans="1:12">
       <c r="B8" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D8" s="3">
         <v>320</v>
@@ -1503,27 +1503,24 @@
         <v>30</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="K8" s="1" t="s">
         <v>39</v>
       </c>
       <c r="L8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:12">
       <c r="B9" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D9" s="3">
         <v>320</v>
@@ -1532,33 +1529,30 @@
         <v>28</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>30</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="J9" s="1" t="s">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L9" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10" spans="1:12">
       <c r="B10" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C10" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D10" s="3">
         <v>320</v>
@@ -1567,33 +1561,30 @@
         <v>27</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I10" s="3">
         <v>601</v>
       </c>
-      <c r="J10" s="1" t="s">
-        <v>32</v>
-      </c>
       <c r="K10" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L10" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="11" spans="1:12">
       <c r="B11" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C11" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D11" s="3">
         <v>330</v>
@@ -1608,27 +1599,24 @@
         <v>30</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="J11" s="1" t="s">
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L11" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="12" spans="1:12">
       <c r="B12" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C12" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D12" s="3">
         <v>260</v>
@@ -1643,27 +1631,24 @@
         <v>30</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="J12" s="1" t="s">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="L12" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="13" spans="1:12">
       <c r="B13" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C13" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D13" s="3">
         <v>330</v>
@@ -1678,27 +1663,24 @@
         <v>30</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="J13" s="1" t="s">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="L13" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="14" spans="1:12">
       <c r="B14" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C14" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D14" s="3">
         <v>330</v>
@@ -1713,19 +1695,16 @@
         <v>30</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="J14" s="1" t="s">
-        <v>32</v>
+        <v>80</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15" spans="1:12">

--- a/Config/HeroConfig.xlsx
+++ b/Config/HeroConfig.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="88">
   <si>
     <t>##var</t>
   </si>
@@ -181,6 +181,9 @@
     <t>401|402|403</t>
   </si>
   <si>
+    <t>105|106|107|108|109|203</t>
+  </si>
+  <si>
     <t>每降低80血量都会使伤害提高5%,最多叠加20层,且攻击时附带8%的吸血;但无法通过圣物回复血量</t>
   </si>
   <si>
@@ -199,6 +202,9 @@
     <t>501|502|503</t>
   </si>
   <si>
+    <t>110|111</t>
+  </si>
+  <si>
     <t>拥有20%暴击率,每击杀1名敌人永久获得3点攻击力,攻击力＞150后,攻击变化为群体伤害;但对领主/精英敌人伤害-25%</t>
   </si>
   <si>
@@ -217,6 +223,9 @@
     <t>People6</t>
   </si>
   <si>
+    <t>112|204</t>
+  </si>
+  <si>
     <t>拥有15%暴击率,攻击时对所有人造成50%的群体伤害;但暴击伤害-50%</t>
   </si>
   <si>
@@ -232,6 +241,9 @@
     <t>701|702|703</t>
   </si>
   <si>
+    <t>113|205</t>
+  </si>
+  <si>
     <t>通过圣物获得的生命回复效果+50%,对精英/领主伤害+50%;但每回合开始时会受到场上当前敌人数量x2的伤害</t>
   </si>
   <si>
@@ -247,6 +259,9 @@
     <t>801|802|803</t>
   </si>
   <si>
+    <t>115|206</t>
+  </si>
+  <si>
     <t>受到伤害-25%,每回合开始会发动1次[圣光燃烧],比牌时若是对子且获得胜利,也会发动[圣光燃烧];但无法闪避(圣光燃烧:对场上所有敌人造成1次当前攻击力50%的伤害,每发动1次会使后续给予伤害+10%)</t>
   </si>
   <si>
@@ -275,6 +290,9 @@
   </si>
   <si>
     <t>1001|1002|1003</t>
+  </si>
+  <si>
+    <t>114</t>
   </si>
   <si>
     <t>拥有25%闪避率,且闪避后会对该敌人进行1次反击,反击伤害为自身攻击力的200%;但每关[搓牌]使用次数-1</t>
@@ -1508,19 +1526,22 @@
       <c r="I8" s="3" t="s">
         <v>48</v>
       </c>
+      <c r="J8" s="1" t="s">
+        <v>49</v>
+      </c>
       <c r="K8" s="1" t="s">
         <v>39</v>
       </c>
       <c r="L8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:12">
       <c r="B9" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D9" s="3">
         <v>320</v>
@@ -1529,30 +1550,33 @@
         <v>28</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>30</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>56</v>
       </c>
       <c r="K9" s="1" t="s">
         <v>45</v>
       </c>
       <c r="L9" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10" spans="1:12">
       <c r="B10" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C10" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D10" s="3">
         <v>320</v>
@@ -1561,30 +1585,33 @@
         <v>27</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="I10" s="3">
         <v>601</v>
       </c>
+      <c r="J10" s="1" t="s">
+        <v>63</v>
+      </c>
       <c r="K10" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="L10" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="11" spans="1:12">
       <c r="B11" s="1" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C11" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D11" s="3">
         <v>330</v>
@@ -1599,24 +1626,27 @@
         <v>30</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>65</v>
+        <v>68</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>69</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="L11" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
     </row>
     <row r="12" spans="1:12">
       <c r="B12" s="1" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C12" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D12" s="3">
         <v>260</v>
@@ -1631,24 +1661,27 @@
         <v>30</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>70</v>
+        <v>74</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>75</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="L12" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
     </row>
     <row r="13" spans="1:12">
       <c r="B13" s="1" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="C13" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D13" s="3">
         <v>330</v>
@@ -1663,24 +1696,24 @@
         <v>30</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="L13" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
     </row>
     <row r="14" spans="1:12">
       <c r="B14" s="1" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="C14" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="D14" s="3">
         <v>330</v>
@@ -1695,16 +1728,19 @@
         <v>30</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>80</v>
+        <v>85</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>86</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
     </row>
     <row r="15" spans="1:12">

--- a/Config/HeroConfig.xlsx
+++ b/Config/HeroConfig.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\cardclient\Config\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\cardclient\Config\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="114">
   <si>
     <t>##var</t>
   </si>
@@ -64,6 +64,33 @@
     <t>HeroEffects</t>
   </si>
   <si>
+    <t>CastEffect</t>
+  </si>
+  <si>
+    <t>SpecialEffect</t>
+  </si>
+  <si>
+    <t>hitAnimation</t>
+  </si>
+  <si>
+    <t>MissAttackEffect</t>
+  </si>
+  <si>
+    <t>HeroEffectsCommon</t>
+  </si>
+  <si>
+    <t>HeroEffectsElite</t>
+  </si>
+  <si>
+    <t>HeroEffectsWeak</t>
+  </si>
+  <si>
+    <t>HeroEffectsMid</t>
+  </si>
+  <si>
+    <t>HeroEffectsStrong</t>
+  </si>
+  <si>
     <t>UnlockCondition</t>
   </si>
   <si>
@@ -109,6 +136,33 @@
     <t>英雄特效Id</t>
   </si>
   <si>
+    <t>施法动作</t>
+  </si>
+  <si>
+    <t>特殊攻击</t>
+  </si>
+  <si>
+    <t>受击动画</t>
+  </si>
+  <si>
+    <t>闪避后的攻击(特殊处理)</t>
+  </si>
+  <si>
+    <t>普通怪受击特效</t>
+  </si>
+  <si>
+    <t>精英受击特效</t>
+  </si>
+  <si>
+    <t>弱档特效Id(释放|命中)，留空回退HeroEffects</t>
+  </si>
+  <si>
+    <t>中档特效Id(释放|命中)</t>
+  </si>
+  <si>
+    <t>强档特效Id(释放|命中)</t>
+  </si>
+  <si>
     <t>解锁难度条件</t>
   </si>
   <si>
@@ -163,7 +217,13 @@
     <t>301|302|303</t>
   </si>
   <si>
-    <t>102|103|104|202</t>
+    <t>103|202</t>
+  </si>
+  <si>
+    <t>102</t>
+  </si>
+  <si>
+    <t>104|202</t>
   </si>
   <si>
     <t>攻击会对其他人造成10%的分裂伤害,每击杀1名敌人该效果就提高3%(精英/领主提高6%);但无法暴击</t>
@@ -184,6 +244,15 @@
     <t>105|106|107|108|109|203</t>
   </si>
   <si>
+    <t>105|203</t>
+  </si>
+  <si>
+    <t>106|208</t>
+  </si>
+  <si>
+    <t>107|209</t>
+  </si>
+  <si>
     <t>每降低80血量都会使伤害提高5%,最多叠加20层,且攻击时附带8%的吸血;但无法通过圣物回复血量</t>
   </si>
   <si>
@@ -244,6 +313,9 @@
     <t>113|205</t>
   </si>
   <si>
+    <t>116|207</t>
+  </si>
+  <si>
     <t>通过圣物获得的生命回复效果+50%,对精英/领主伤害+50%;但每回合开始时会受到场上当前敌人数量x2的伤害</t>
   </si>
   <si>
@@ -262,6 +334,9 @@
     <t>115|206</t>
   </si>
   <si>
+    <t>ani_sqs_gj_hit</t>
+  </si>
+  <si>
     <t>受到伤害-25%,每回合开始会发动1次[圣光燃烧],比牌时若是对子且获得胜利,也会发动[圣光燃烧];但无法闪避(圣光燃烧:对场上所有敌人造成1次当前攻击力50%的伤害,每发动1次会使后续给予伤害+10%)</t>
   </si>
   <si>
@@ -290,6 +365,9 @@
   </si>
   <si>
     <t>1001|1002|1003</t>
+  </si>
+  <si>
+    <t>ani_ws_gj_hit</t>
   </si>
   <si>
     <t>114</t>
@@ -1270,7 +1348,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L15"/>
+  <dimension ref="A1:U15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="3.075" style="1" customWidth="1"/>
@@ -1281,15 +1359,15 @@
     <col min="6" max="6" width="6.35" style="1" customWidth="1"/>
     <col min="7" max="7" width="7.88333333333333" style="1" customWidth="1"/>
     <col min="8" max="8" width="12" style="1" customWidth="1"/>
-    <col min="9" max="9" width="13.75" style="3" customWidth="1"/>
-    <col min="10" max="10" width="11" style="1" customWidth="1"/>
-    <col min="11" max="11" width="4.41666666666667" style="1" customWidth="1"/>
-    <col min="12" max="12" width="14.375" style="1" customWidth="1"/>
-    <col min="13" max="13" width="34.75" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="9" style="1" customWidth="1"/>
+    <col min="9" max="9" width="16" style="3" customWidth="1"/>
+    <col min="10" max="16" width="26" style="1" customWidth="1"/>
+    <col min="17" max="17" width="17.125" style="1" customWidth="1"/>
+    <col min="18" max="18" width="14.375" style="1" customWidth="1"/>
+    <col min="19" max="19" width="34.75" style="1" customWidth="1"/>
+    <col min="20" max="16384" width="9" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:21">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1326,90 +1404,171 @@
       <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:21">
       <c r="A2" s="1" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>14</v>
+        <v>25</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="R2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="S2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="T2" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="U2" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:12">
+    <row r="3" spans="1:21">
       <c r="A3" s="1" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>26</v>
+        <v>35</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="R3" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="S3" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="T3" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="U3" s="1" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1"/>
-    <row r="5" spans="1:12">
+    <row r="5" spans="1:21">
       <c r="B5" s="1" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="C5" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="D5" s="3">
         <v>320</v>
@@ -1418,25 +1577,25 @@
         <v>40</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="I5" s="1"/>
-      <c r="L5" s="1" t="s">
-        <v>32</v>
+      <c r="U5" s="1" t="s">
+        <v>50</v>
       </c>
     </row>
-    <row r="6" spans="1:12">
+    <row r="6" spans="1:21">
       <c r="B6" s="1" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="C6" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="D6" s="3">
         <v>370</v>
@@ -1445,33 +1604,33 @@
         <v>27</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="L6" t="s">
-        <v>38</v>
+        <v>55</v>
+      </c>
+      <c r="T6" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="U6" t="s">
+        <v>56</v>
       </c>
     </row>
-    <row r="7" spans="1:12">
+    <row r="7" spans="1:21">
       <c r="B7" s="1" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="C7" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="D7" s="3">
         <v>320</v>
@@ -1480,33 +1639,39 @@
         <v>30</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="L7" t="s">
-        <v>44</v>
+        <v>62</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="T7" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="U7" t="s">
+        <v>64</v>
       </c>
     </row>
-    <row r="8" spans="1:12">
+    <row r="8" spans="1:21">
       <c r="B8" s="1" t="s">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="C8" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="D8" s="3">
         <v>320</v>
@@ -1515,33 +1680,42 @@
         <v>31</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="L8" t="s">
-        <v>50</v>
+        <v>69</v>
+      </c>
+      <c r="Q8" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="R8" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="S8" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="T8" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="U8" t="s">
+        <v>73</v>
       </c>
     </row>
-    <row r="9" spans="1:12">
+    <row r="9" spans="1:21">
       <c r="B9" s="1" t="s">
-        <v>51</v>
+        <v>74</v>
       </c>
       <c r="C9" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="D9" s="3">
         <v>320</v>
@@ -1550,33 +1724,33 @@
         <v>28</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>53</v>
+        <v>76</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>54</v>
+        <v>77</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>55</v>
+        <v>78</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="K9" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="L9" t="s">
-        <v>57</v>
+        <v>79</v>
+      </c>
+      <c r="T9" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="U9" t="s">
+        <v>80</v>
       </c>
     </row>
-    <row r="10" spans="1:12">
+    <row r="10" spans="1:21">
       <c r="B10" s="1" t="s">
-        <v>58</v>
+        <v>81</v>
       </c>
       <c r="C10" t="s">
-        <v>59</v>
+        <v>82</v>
       </c>
       <c r="D10" s="3">
         <v>320</v>
@@ -1585,33 +1759,33 @@
         <v>27</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>61</v>
+        <v>84</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>62</v>
+        <v>85</v>
       </c>
       <c r="I10" s="3">
         <v>601</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="K10" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="L10" t="s">
-        <v>64</v>
+        <v>86</v>
+      </c>
+      <c r="T10" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="U10" t="s">
+        <v>87</v>
       </c>
     </row>
-    <row r="11" spans="1:12">
+    <row r="11" spans="1:21">
       <c r="B11" s="1" t="s">
-        <v>65</v>
+        <v>88</v>
       </c>
       <c r="C11" t="s">
-        <v>66</v>
+        <v>89</v>
       </c>
       <c r="D11" s="3">
         <v>330</v>
@@ -1620,33 +1794,39 @@
         <v>33</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>67</v>
+        <v>90</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="K11" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="L11" t="s">
-        <v>70</v>
+        <v>92</v>
+      </c>
+      <c r="O11" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="P11" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="T11" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="U11" t="s">
+        <v>94</v>
       </c>
     </row>
-    <row r="12" spans="1:12">
+    <row r="12" spans="1:21">
       <c r="B12" s="1" t="s">
-        <v>71</v>
+        <v>95</v>
       </c>
       <c r="C12" t="s">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="D12" s="3">
         <v>260</v>
@@ -1655,33 +1835,36 @@
         <v>30</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>73</v>
+        <v>97</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="K12" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="L12" t="s">
-        <v>76</v>
+        <v>99</v>
+      </c>
+      <c r="M12" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="T12" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="U12" t="s">
+        <v>101</v>
       </c>
     </row>
-    <row r="13" spans="1:12">
+    <row r="13" spans="1:21">
       <c r="B13" s="1" t="s">
-        <v>77</v>
+        <v>102</v>
       </c>
       <c r="C13" t="s">
-        <v>78</v>
+        <v>103</v>
       </c>
       <c r="D13" s="3">
         <v>330</v>
@@ -1690,30 +1873,30 @@
         <v>38</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>79</v>
+        <v>104</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="K13" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="L13" t="s">
-        <v>81</v>
+        <v>105</v>
+      </c>
+      <c r="T13" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="U13" t="s">
+        <v>106</v>
       </c>
     </row>
-    <row r="14" spans="1:12">
+    <row r="14" spans="1:21">
       <c r="B14" s="1" t="s">
-        <v>82</v>
+        <v>107</v>
       </c>
       <c r="C14" t="s">
-        <v>83</v>
+        <v>108</v>
       </c>
       <c r="D14" s="3">
         <v>330</v>
@@ -1722,28 +1905,31 @@
         <v>33</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>84</v>
+        <v>109</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="J14" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="K14" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="L14" s="1" t="s">
-        <v>87</v>
+        <v>110</v>
+      </c>
+      <c r="M14" t="s">
+        <v>111</v>
+      </c>
+      <c r="N14" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="T14" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="U14" s="1" t="s">
+        <v>113</v>
       </c>
     </row>
-    <row r="15" spans="1:12">
+    <row r="15" spans="1:21">
       <c r="C15"/>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>

--- a/Config/HeroConfig.xlsx
+++ b/Config/HeroConfig.xlsx
@@ -1846,7 +1846,7 @@
       <c r="I12" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="J12" s="1" t="s">
+      <c r="L12" s="1" t="s">
         <v>99</v>
       </c>
       <c r="M12" s="1" t="s">
